--- a/research/traditional_assets/database/data/netherlands/netherlands_household_products.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07509751830440489</v>
+        <v>0.07493715670717951</v>
       </c>
       <c r="C2">
-        <v>22.10692564868984</v>
+        <v>21.94204139359706</v>
       </c>
       <c r="D2">
-        <v>21.64292564868984</v>
+        <v>21.76204139359706</v>
       </c>
       <c r="E2">
-        <v>-17.9</v>
+        <v>-17.616</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.284</v>
       </c>
       <c r="G2">
         <v>0.464</v>
@@ -1451,28 +1451,28 @@
         <v>1.27</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0142852</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>1.2557148</v>
       </c>
       <c r="O2">
-        <v>0.32766</v>
+        <v>0.3239744184</v>
       </c>
       <c r="P2">
-        <v>0.9423399999999998</v>
+        <v>0.9317403815999998</v>
       </c>
       <c r="Q2">
-        <v>1.97234</v>
+        <v>1.9617403816</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07509751830440489</v>
+        <v>0.07531710172442375</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6816882615340361</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>88.90320051521854</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07493715670717951</v>
+        <v>0.07477679510995415</v>
       </c>
       <c r="C3">
-        <v>21.94204139359706</v>
+        <v>21.77847554456232</v>
       </c>
       <c r="D3">
-        <v>21.76204139359706</v>
+        <v>21.88247554456232</v>
       </c>
       <c r="E3">
-        <v>-17.616</v>
+        <v>-17.332</v>
       </c>
       <c r="F3">
-        <v>0.284</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G3">
         <v>0.464</v>
@@ -1533,28 +1533,28 @@
         <v>1.27</v>
       </c>
       <c r="M3">
-        <v>0.0142852</v>
+        <v>0.0285704</v>
       </c>
       <c r="N3">
-        <v>1.2557148</v>
+        <v>1.2414296</v>
       </c>
       <c r="O3">
-        <v>0.3239744184</v>
+        <v>0.3202888368</v>
       </c>
       <c r="P3">
-        <v>0.9317403815999998</v>
+        <v>0.9211407631999998</v>
       </c>
       <c r="Q3">
-        <v>1.9617403816</v>
+        <v>1.9511407632</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07531710172442375</v>
+        <v>0.07554116643872873</v>
       </c>
       <c r="T3">
-        <v>0.6816882615340361</v>
+        <v>0.6868629662523957</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>88.90320051521854</v>
+        <v>44.45160025760927</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07477679510995415</v>
+        <v>0.07461643351272877</v>
       </c>
       <c r="C4">
-        <v>21.77847554456232</v>
+        <v>21.61625011212015</v>
       </c>
       <c r="D4">
-        <v>21.88247554456232</v>
+        <v>22.00425011212015</v>
       </c>
       <c r="E4">
-        <v>-17.332</v>
+        <v>-17.048</v>
       </c>
       <c r="F4">
-        <v>0.5679999999999999</v>
+        <v>0.852</v>
       </c>
       <c r="G4">
         <v>0.464</v>
@@ -1615,28 +1615,28 @@
         <v>1.27</v>
       </c>
       <c r="M4">
-        <v>0.0285704</v>
+        <v>0.04285559999999999</v>
       </c>
       <c r="N4">
-        <v>1.2414296</v>
+        <v>1.2271444</v>
       </c>
       <c r="O4">
-        <v>0.3202888368</v>
+        <v>0.3166032551999999</v>
       </c>
       <c r="P4">
-        <v>0.9211407631999998</v>
+        <v>0.9105411447999998</v>
       </c>
       <c r="Q4">
-        <v>1.9511407632</v>
+        <v>1.9405411448</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07554116643872873</v>
+        <v>0.07576985104405029</v>
       </c>
       <c r="T4">
-        <v>0.6868629662523957</v>
+        <v>0.6921443659134019</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>44.45160025760927</v>
+        <v>29.63440017173951</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07461643351272877</v>
+        <v>0.07445607191550342</v>
       </c>
       <c r="C5">
-        <v>21.61625011212015</v>
+        <v>21.45538759949561</v>
       </c>
       <c r="D5">
-        <v>22.00425011212015</v>
+        <v>22.12738759949561</v>
       </c>
       <c r="E5">
-        <v>-17.048</v>
+        <v>-16.764</v>
       </c>
       <c r="F5">
-        <v>0.852</v>
+        <v>1.136</v>
       </c>
       <c r="G5">
         <v>0.464</v>
@@ -1697,28 +1697,28 @@
         <v>1.27</v>
       </c>
       <c r="M5">
-        <v>0.04285559999999999</v>
+        <v>0.05714079999999999</v>
       </c>
       <c r="N5">
-        <v>1.2271444</v>
+        <v>1.2128592</v>
       </c>
       <c r="O5">
-        <v>0.3166032551999999</v>
+        <v>0.3129176735999999</v>
       </c>
       <c r="P5">
-        <v>0.9105411447999998</v>
+        <v>0.8999415263999999</v>
       </c>
       <c r="Q5">
-        <v>1.9405411448</v>
+        <v>1.9299415264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07576985104405029</v>
+        <v>0.07600329991198274</v>
       </c>
       <c r="T5">
-        <v>0.6921443659134019</v>
+        <v>0.6975357947340125</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>29.63440017173951</v>
+        <v>22.22580012880464</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07445607191550342</v>
+        <v>0.07429571031827804</v>
       </c>
       <c r="C6">
-        <v>21.45538759949561</v>
+        <v>21.29591101646774</v>
       </c>
       <c r="D6">
-        <v>22.12738759949561</v>
+        <v>22.25191101646774</v>
       </c>
       <c r="E6">
-        <v>-16.764</v>
+        <v>-16.48</v>
       </c>
       <c r="F6">
-        <v>1.136</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
         <v>0.464</v>
@@ -1779,28 +1779,28 @@
         <v>1.27</v>
       </c>
       <c r="M6">
-        <v>0.05714079999999999</v>
+        <v>0.07142599999999999</v>
       </c>
       <c r="N6">
-        <v>1.2128592</v>
+        <v>1.198574</v>
       </c>
       <c r="O6">
-        <v>0.3129176735999999</v>
+        <v>0.309232092</v>
       </c>
       <c r="P6">
-        <v>0.8999415263999999</v>
+        <v>0.8893419079999998</v>
       </c>
       <c r="Q6">
-        <v>1.9299415264</v>
+        <v>1.919341908</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07600329991198274</v>
+        <v>0.07624166349292427</v>
       </c>
       <c r="T6">
-        <v>0.6975357947340125</v>
+        <v>0.7030407273192675</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.22580012880464</v>
+        <v>17.78064010304371</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07429571031827804</v>
+        <v>0.07413534872105269</v>
       </c>
       <c r="C7">
-        <v>21.29591101646774</v>
+        <v>21.13784389370338</v>
       </c>
       <c r="D7">
-        <v>22.25191101646774</v>
+        <v>22.37784389370338</v>
       </c>
       <c r="E7">
-        <v>-16.48</v>
+        <v>-16.196</v>
       </c>
       <c r="F7">
-        <v>1.42</v>
+        <v>1.704</v>
       </c>
       <c r="G7">
         <v>0.464</v>
@@ -1861,28 +1861,28 @@
         <v>1.27</v>
       </c>
       <c r="M7">
-        <v>0.07142599999999999</v>
+        <v>0.08571119999999999</v>
       </c>
       <c r="N7">
-        <v>1.198574</v>
+        <v>1.1842888</v>
       </c>
       <c r="O7">
-        <v>0.309232092</v>
+        <v>0.3055465104</v>
       </c>
       <c r="P7">
-        <v>0.8893419079999998</v>
+        <v>0.8787422895999999</v>
       </c>
       <c r="Q7">
-        <v>1.919341908</v>
+        <v>1.9087422896</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07624166349292427</v>
+        <v>0.07648509863941777</v>
       </c>
       <c r="T7">
-        <v>0.7030407273192675</v>
+        <v>0.7086627861297407</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.78064010304371</v>
+        <v>14.81720008586976</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07413534872105269</v>
+        <v>0.07405289712382734</v>
       </c>
       <c r="C8">
-        <v>21.13784389370338</v>
+        <v>20.91915008030112</v>
       </c>
       <c r="D8">
-        <v>22.37784389370338</v>
+        <v>22.44315008030112</v>
       </c>
       <c r="E8">
-        <v>-16.196</v>
+        <v>-15.912</v>
       </c>
       <c r="F8">
-        <v>1.704</v>
+        <v>1.988</v>
       </c>
       <c r="G8">
         <v>0.464</v>
@@ -1943,45 +1943,45 @@
         <v>1.27</v>
       </c>
       <c r="M8">
-        <v>0.08571119999999999</v>
+        <v>0.1029784</v>
       </c>
       <c r="N8">
-        <v>1.1842888</v>
+        <v>1.1670216</v>
       </c>
       <c r="O8">
-        <v>0.3055465104</v>
+        <v>0.3010915727999999</v>
       </c>
       <c r="P8">
-        <v>0.8787422895999999</v>
+        <v>0.8659300271999999</v>
       </c>
       <c r="Q8">
-        <v>1.9087422896</v>
+        <v>1.8959300272</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07648509863941777</v>
+        <v>0.07673376895035197</v>
       </c>
       <c r="T8">
-        <v>0.7086627861297407</v>
+        <v>0.7144057494307616</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.81720008586976</v>
+        <v>12.3326833588403</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07405289712382733</v>
+        <v>0.07390366552660198</v>
       </c>
       <c r="C9">
-        <v>20.91915008030113</v>
+        <v>20.75432411224658</v>
       </c>
       <c r="D9">
-        <v>22.44315008030113</v>
+        <v>22.56232411224658</v>
       </c>
       <c r="E9">
-        <v>-15.912</v>
+        <v>-15.628</v>
       </c>
       <c r="F9">
-        <v>1.988</v>
+        <v>2.272</v>
       </c>
       <c r="G9">
         <v>0.464</v>
@@ -2025,28 +2025,28 @@
         <v>1.27</v>
       </c>
       <c r="M9">
-        <v>0.1029784</v>
+        <v>0.1176896</v>
       </c>
       <c r="N9">
-        <v>1.1670216</v>
+        <v>1.1523104</v>
       </c>
       <c r="O9">
-        <v>0.3010915727999999</v>
+        <v>0.2972960831999999</v>
       </c>
       <c r="P9">
-        <v>0.8659300271999999</v>
+        <v>0.8550143167999997</v>
       </c>
       <c r="Q9">
-        <v>1.8959300272</v>
+        <v>1.8850143168</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07673376895035197</v>
+        <v>0.07698784513761084</v>
       </c>
       <c r="T9">
-        <v>0.7144057494307616</v>
+        <v>0.7202735597600656</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.3326833588403</v>
+        <v>10.79109793898526</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07390366552660198</v>
+        <v>0.0738679599293766</v>
       </c>
       <c r="C10">
-        <v>20.75432411224658</v>
+        <v>20.49902592239763</v>
       </c>
       <c r="D10">
-        <v>22.56232411224658</v>
+        <v>22.59102592239763</v>
       </c>
       <c r="E10">
-        <v>-15.628</v>
+        <v>-15.344</v>
       </c>
       <c r="F10">
-        <v>2.272</v>
+        <v>2.556</v>
       </c>
       <c r="G10">
         <v>0.464</v>
@@ -2107,45 +2107,45 @@
         <v>1.27</v>
       </c>
       <c r="M10">
-        <v>0.1176896</v>
+        <v>0.136746</v>
       </c>
       <c r="N10">
-        <v>1.1523104</v>
+        <v>1.133254</v>
       </c>
       <c r="O10">
-        <v>0.2972960831999999</v>
+        <v>0.2923795319999999</v>
       </c>
       <c r="P10">
-        <v>0.8550143167999997</v>
+        <v>0.8408744679999998</v>
       </c>
       <c r="Q10">
-        <v>1.8850143168</v>
+        <v>1.870874468</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07698784513761084</v>
+        <v>0.07724750541689737</v>
       </c>
       <c r="T10">
-        <v>0.7202735597600656</v>
+        <v>0.7262703329537499</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.79109793898526</v>
+        <v>9.287291767218054</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0738679599293766</v>
+        <v>0.07373134233215123</v>
       </c>
       <c r="C11">
-        <v>20.49902592239763</v>
+        <v>20.32552299925388</v>
       </c>
       <c r="D11">
-        <v>22.59102592239763</v>
+        <v>22.70152299925389</v>
       </c>
       <c r="E11">
-        <v>-15.344</v>
+        <v>-15.06</v>
       </c>
       <c r="F11">
-        <v>2.556</v>
+        <v>2.839999999999999</v>
       </c>
       <c r="G11">
         <v>0.464</v>
@@ -2189,28 +2189,28 @@
         <v>1.27</v>
       </c>
       <c r="M11">
-        <v>0.136746</v>
+        <v>0.15194</v>
       </c>
       <c r="N11">
-        <v>1.133254</v>
+        <v>1.11806</v>
       </c>
       <c r="O11">
-        <v>0.2923795319999999</v>
+        <v>0.28845948</v>
       </c>
       <c r="P11">
-        <v>0.8408744679999998</v>
+        <v>0.8296005199999998</v>
       </c>
       <c r="Q11">
-        <v>1.870874468</v>
+        <v>1.85960052</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07724750541689737</v>
+        <v>0.07751293592461249</v>
       </c>
       <c r="T11">
-        <v>0.7262703329537499</v>
+        <v>0.7324003677739607</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.287291767218054</v>
+        <v>8.358562590496248</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07373134233215123</v>
+        <v>0.07366002073492588</v>
       </c>
       <c r="C12">
-        <v>20.32552299925388</v>
+        <v>20.0996388526181</v>
       </c>
       <c r="D12">
-        <v>22.70152299925389</v>
+        <v>22.7596388526181</v>
       </c>
       <c r="E12">
-        <v>-15.06</v>
+        <v>-14.776</v>
       </c>
       <c r="F12">
-        <v>2.84</v>
+        <v>3.124</v>
       </c>
       <c r="G12">
         <v>0.464</v>
@@ -2271,45 +2271,45 @@
         <v>1.27</v>
       </c>
       <c r="M12">
-        <v>0.15194</v>
+        <v>0.1696332</v>
       </c>
       <c r="N12">
-        <v>1.11806</v>
+        <v>1.1003668</v>
       </c>
       <c r="O12">
-        <v>0.28845948</v>
+        <v>0.2838946344</v>
       </c>
       <c r="P12">
-        <v>0.8296005199999998</v>
+        <v>0.8164721655999998</v>
       </c>
       <c r="Q12">
-        <v>1.85960052</v>
+        <v>1.8464721656</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07751293592461249</v>
+        <v>0.07778433116283806</v>
       </c>
       <c r="T12">
-        <v>0.7324003677739607</v>
+        <v>0.7386681561856365</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.358562590496248</v>
+        <v>7.486741982111991</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07366002073492588</v>
+        <v>0.07352933913770052</v>
       </c>
       <c r="C13">
-        <v>20.0996388526181</v>
+        <v>19.92289946718819</v>
       </c>
       <c r="D13">
-        <v>22.7596388526181</v>
+        <v>22.8668994671882</v>
       </c>
       <c r="E13">
-        <v>-14.776</v>
+        <v>-14.492</v>
       </c>
       <c r="F13">
-        <v>3.124</v>
+        <v>3.408</v>
       </c>
       <c r="G13">
         <v>0.464</v>
@@ -2353,28 +2353,28 @@
         <v>1.27</v>
       </c>
       <c r="M13">
-        <v>0.1696332</v>
+        <v>0.1850544</v>
       </c>
       <c r="N13">
-        <v>1.1003668</v>
+        <v>1.0849456</v>
       </c>
       <c r="O13">
-        <v>0.2838946344</v>
+        <v>0.2799159647999999</v>
       </c>
       <c r="P13">
-        <v>0.8164721655999998</v>
+        <v>0.8050296351999998</v>
       </c>
       <c r="Q13">
-        <v>1.8464721656</v>
+        <v>1.8350296352</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07778433116283806</v>
+        <v>0.07806189447465967</v>
       </c>
       <c r="T13">
-        <v>0.7386681561856365</v>
+        <v>0.7450783943339417</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.486741982111991</v>
+        <v>6.862846816935991</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07352933913770052</v>
+        <v>0.07339865754047514</v>
       </c>
       <c r="C14">
-        <v>19.92289946718819</v>
+        <v>19.74717585496473</v>
       </c>
       <c r="D14">
-        <v>22.8668994671882</v>
+        <v>22.97517585496473</v>
       </c>
       <c r="E14">
-        <v>-14.492</v>
+        <v>-14.208</v>
       </c>
       <c r="F14">
-        <v>3.408</v>
+        <v>3.692</v>
       </c>
       <c r="G14">
         <v>0.464</v>
@@ -2435,28 +2435,28 @@
         <v>1.27</v>
       </c>
       <c r="M14">
-        <v>0.1850544</v>
+        <v>0.2004756</v>
       </c>
       <c r="N14">
-        <v>1.0849456</v>
+        <v>1.0695244</v>
       </c>
       <c r="O14">
-        <v>0.2799159647999999</v>
+        <v>0.2759372951999999</v>
       </c>
       <c r="P14">
-        <v>0.8050296351999998</v>
+        <v>0.7935871047999998</v>
       </c>
       <c r="Q14">
-        <v>1.8350296352</v>
+        <v>1.8235871048</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07806189447465967</v>
+        <v>0.07834583855227029</v>
       </c>
       <c r="T14">
-        <v>0.7450783943339417</v>
+        <v>0.7516359942787595</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.862846816935991</v>
+        <v>6.334935523325531</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07339865754047514</v>
+        <v>0.07337185594324977</v>
       </c>
       <c r="C15">
-        <v>19.74717585496473</v>
+        <v>19.48550918684904</v>
       </c>
       <c r="D15">
-        <v>22.97517585496473</v>
+        <v>22.99750918684904</v>
       </c>
       <c r="E15">
-        <v>-14.208</v>
+        <v>-13.924</v>
       </c>
       <c r="F15">
-        <v>3.692</v>
+        <v>3.976</v>
       </c>
       <c r="G15">
         <v>0.464</v>
@@ -2517,45 +2517,45 @@
         <v>1.27</v>
       </c>
       <c r="M15">
-        <v>0.2004756</v>
+        <v>0.2198728</v>
       </c>
       <c r="N15">
-        <v>1.0695244</v>
+        <v>1.0501272</v>
       </c>
       <c r="O15">
-        <v>0.2759372951999999</v>
+        <v>0.2709328175999999</v>
       </c>
       <c r="P15">
-        <v>0.7935871047999998</v>
+        <v>0.7791943823999998</v>
       </c>
       <c r="Q15">
-        <v>1.8235871048</v>
+        <v>1.8091943824</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07834583855227029</v>
+        <v>0.078636385980523</v>
       </c>
       <c r="T15">
-        <v>0.7516359942787595</v>
+        <v>0.7583460965478754</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.334935523325531</v>
+        <v>5.77606688958343</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07337185594324977</v>
+        <v>0.0732485943460244</v>
       </c>
       <c r="C16">
-        <v>19.48550918684904</v>
+        <v>19.30478258871585</v>
       </c>
       <c r="D16">
-        <v>22.99750918684904</v>
+        <v>23.10078258871585</v>
       </c>
       <c r="E16">
-        <v>-13.924</v>
+        <v>-13.64</v>
       </c>
       <c r="F16">
-        <v>3.976</v>
+        <v>4.260000000000001</v>
       </c>
       <c r="G16">
         <v>0.464</v>
@@ -2599,28 +2599,28 @@
         <v>1.27</v>
       </c>
       <c r="M16">
-        <v>0.2198728</v>
+        <v>0.235578</v>
       </c>
       <c r="N16">
-        <v>1.0501272</v>
+        <v>1.034422</v>
       </c>
       <c r="O16">
-        <v>0.2709328175999999</v>
+        <v>0.2668808759999999</v>
       </c>
       <c r="P16">
-        <v>0.7791943823999998</v>
+        <v>0.7675411239999999</v>
       </c>
       <c r="Q16">
-        <v>1.8091943824</v>
+        <v>1.797541124</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.078636385980523</v>
+        <v>0.07893376981885225</v>
       </c>
       <c r="T16">
-        <v>0.7583460965478754</v>
+        <v>0.7652140835762647</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.77606688958343</v>
+        <v>5.390995763611201</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0732485943460244</v>
+        <v>0.07312533274879904</v>
       </c>
       <c r="C17">
-        <v>19.30478258871585</v>
+        <v>19.1249877006981</v>
       </c>
       <c r="D17">
-        <v>23.10078258871585</v>
+        <v>23.2049877006981</v>
       </c>
       <c r="E17">
-        <v>-13.64</v>
+        <v>-13.356</v>
       </c>
       <c r="F17">
-        <v>4.26</v>
+        <v>4.544</v>
       </c>
       <c r="G17">
         <v>0.464</v>
@@ -2681,28 +2681,28 @@
         <v>1.27</v>
       </c>
       <c r="M17">
-        <v>0.235578</v>
+        <v>0.2512832</v>
       </c>
       <c r="N17">
-        <v>1.034422</v>
+        <v>1.0187168</v>
       </c>
       <c r="O17">
-        <v>0.2668808759999999</v>
+        <v>0.2628289343999999</v>
       </c>
       <c r="P17">
-        <v>0.7675411239999999</v>
+        <v>0.7558878655999999</v>
       </c>
       <c r="Q17">
-        <v>1.797541124</v>
+        <v>1.7858878656</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07893376981885225</v>
+        <v>0.07923823422476077</v>
       </c>
       <c r="T17">
-        <v>0.7652140835762647</v>
+        <v>0.7722455941053298</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.390995763611202</v>
+        <v>5.054058528385502</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07312533274879904</v>
+        <v>0.07300207115157369</v>
       </c>
       <c r="C18">
-        <v>19.1249877006981</v>
+        <v>18.9461371884575</v>
       </c>
       <c r="D18">
-        <v>23.2049877006981</v>
+        <v>23.3101371884575</v>
       </c>
       <c r="E18">
-        <v>-13.356</v>
+        <v>-13.072</v>
       </c>
       <c r="F18">
-        <v>4.544</v>
+        <v>4.828</v>
       </c>
       <c r="G18">
         <v>0.464</v>
@@ -2763,28 +2763,28 @@
         <v>1.27</v>
       </c>
       <c r="M18">
-        <v>0.2512832</v>
+        <v>0.2669884</v>
       </c>
       <c r="N18">
-        <v>1.0187168</v>
+        <v>1.0030116</v>
       </c>
       <c r="O18">
-        <v>0.2628289343999999</v>
+        <v>0.2587769927999999</v>
       </c>
       <c r="P18">
-        <v>0.7558878655999999</v>
+        <v>0.7442346071999999</v>
       </c>
       <c r="Q18">
-        <v>1.7858878656</v>
+        <v>1.7742346072</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07923823422476077</v>
+        <v>0.07955003512237793</v>
       </c>
       <c r="T18">
-        <v>0.7722455941053298</v>
+        <v>0.7794465386230472</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.054058528385502</v>
+        <v>4.756760967892237</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07300207115157369</v>
+        <v>0.07321270955434832</v>
       </c>
       <c r="C19">
-        <v>18.9461371884575</v>
+        <v>18.48302282341819</v>
       </c>
       <c r="D19">
-        <v>23.3101371884575</v>
+        <v>23.13102282341819</v>
       </c>
       <c r="E19">
-        <v>-13.072</v>
+        <v>-12.788</v>
       </c>
       <c r="F19">
-        <v>4.828</v>
+        <v>5.112</v>
       </c>
       <c r="G19">
         <v>0.464</v>
@@ -2845,45 +2845,45 @@
         <v>1.27</v>
       </c>
       <c r="M19">
-        <v>0.2669884</v>
+        <v>0.2954736</v>
       </c>
       <c r="N19">
-        <v>1.0030116</v>
+        <v>0.9745263999999998</v>
       </c>
       <c r="O19">
-        <v>0.2587769927999999</v>
+        <v>0.2514278112</v>
       </c>
       <c r="P19">
-        <v>0.7442346071999999</v>
+        <v>0.7230985887999999</v>
       </c>
       <c r="Q19">
-        <v>1.7742346072</v>
+        <v>1.7530985888</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07955003512237793</v>
+        <v>0.07986944091993697</v>
       </c>
       <c r="T19">
-        <v>0.7794465386230472</v>
+        <v>0.7868231159338794</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.756760967892237</v>
+        <v>4.298184338634652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07321270955434833</v>
+        <v>0.07310799795712296</v>
       </c>
       <c r="C20">
-        <v>18.48302282341818</v>
+        <v>18.28771795035863</v>
       </c>
       <c r="D20">
-        <v>23.13102282341818</v>
+        <v>23.21971795035863</v>
       </c>
       <c r="E20">
-        <v>-12.788</v>
+        <v>-12.504</v>
       </c>
       <c r="F20">
-        <v>5.111999999999999</v>
+        <v>5.396</v>
       </c>
       <c r="G20">
         <v>0.464</v>
@@ -2927,28 +2927,28 @@
         <v>1.27</v>
       </c>
       <c r="M20">
-        <v>0.2954736</v>
+        <v>0.3118888</v>
       </c>
       <c r="N20">
-        <v>0.9745263999999998</v>
+        <v>0.9581111999999998</v>
       </c>
       <c r="O20">
-        <v>0.2514278112</v>
+        <v>0.2471926896</v>
       </c>
       <c r="P20">
-        <v>0.7230985887999999</v>
+        <v>0.7109185103999999</v>
       </c>
       <c r="Q20">
-        <v>1.7530985888</v>
+        <v>1.7409185104</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07986944091993697</v>
+        <v>0.08019673328039871</v>
       </c>
       <c r="T20">
-        <v>0.7868231159338794</v>
+        <v>0.7943818309560905</v>
       </c>
       <c r="U20">
         <v>0.0578</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.298184338634652</v>
+        <v>4.07196411028546</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07310799795712296</v>
+        <v>0.07352268635989759</v>
       </c>
       <c r="C21">
-        <v>18.28771795035863</v>
+        <v>17.65638697295233</v>
       </c>
       <c r="D21">
-        <v>23.21971795035863</v>
+        <v>22.87238697295233</v>
       </c>
       <c r="E21">
-        <v>-12.504</v>
+        <v>-12.22</v>
       </c>
       <c r="F21">
-        <v>5.396</v>
+        <v>5.68</v>
       </c>
       <c r="G21">
         <v>0.464</v>
@@ -3009,45 +3009,45 @@
         <v>1.27</v>
       </c>
       <c r="M21">
-        <v>0.3118888</v>
+        <v>0.348184</v>
       </c>
       <c r="N21">
-        <v>0.9581111999999998</v>
+        <v>0.9218159999999997</v>
       </c>
       <c r="O21">
-        <v>0.2471926896</v>
+        <v>0.2378285279999999</v>
       </c>
       <c r="P21">
-        <v>0.7109185103999999</v>
+        <v>0.6839874719999999</v>
       </c>
       <c r="Q21">
-        <v>1.7409185104</v>
+        <v>1.713987472</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08019673328039871</v>
+        <v>0.080532207949872</v>
       </c>
       <c r="T21">
-        <v>0.7943818309560905</v>
+        <v>0.8021295138538568</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.07196411028546</v>
+        <v>3.64749672586908</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07352268635989759</v>
+        <v>0.07388024076267224</v>
       </c>
       <c r="C22">
-        <v>17.65638697295233</v>
+        <v>17.08114578548302</v>
       </c>
       <c r="D22">
-        <v>22.87238697295233</v>
+        <v>22.58114578548302</v>
       </c>
       <c r="E22">
-        <v>-12.22</v>
+        <v>-11.936</v>
       </c>
       <c r="F22">
-        <v>5.68</v>
+        <v>5.964</v>
       </c>
       <c r="G22">
         <v>0.464</v>
@@ -3091,45 +3091,45 @@
         <v>1.27</v>
       </c>
       <c r="M22">
-        <v>0.348184</v>
+        <v>0.3822924</v>
       </c>
       <c r="N22">
-        <v>0.9218159999999997</v>
+        <v>0.8877075999999997</v>
       </c>
       <c r="O22">
-        <v>0.2378285279999999</v>
+        <v>0.2290285607999999</v>
       </c>
       <c r="P22">
-        <v>0.6839874719999999</v>
+        <v>0.6586790391999998</v>
       </c>
       <c r="Q22">
-        <v>1.713987472</v>
+        <v>1.6886790392</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.080532207949872</v>
+        <v>0.08087617564895219</v>
       </c>
       <c r="T22">
-        <v>0.8021295138538568</v>
+        <v>0.8100733406224526</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.64749672586908</v>
+        <v>3.322064472116107</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07388024076267224</v>
+        <v>0.07382227516544687</v>
       </c>
       <c r="C23">
-        <v>17.08114578548302</v>
+        <v>16.8438561112421</v>
       </c>
       <c r="D23">
-        <v>22.58114578548302</v>
+        <v>22.6278561112421</v>
       </c>
       <c r="E23">
-        <v>-11.936</v>
+        <v>-11.652</v>
       </c>
       <c r="F23">
-        <v>5.964</v>
+        <v>6.247999999999999</v>
       </c>
       <c r="G23">
         <v>0.464</v>
@@ -3173,28 +3173,28 @@
         <v>1.27</v>
       </c>
       <c r="M23">
-        <v>0.3822924</v>
+        <v>0.4004968</v>
       </c>
       <c r="N23">
-        <v>0.8877075999999998</v>
+        <v>0.8695031999999998</v>
       </c>
       <c r="O23">
-        <v>0.2290285607999999</v>
+        <v>0.2243318256</v>
       </c>
       <c r="P23">
-        <v>0.6586790391999999</v>
+        <v>0.6451713743999998</v>
       </c>
       <c r="Q23">
-        <v>1.6886790392</v>
+        <v>1.6751713744</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08087617564895219</v>
+        <v>0.08122896303262418</v>
       </c>
       <c r="T23">
-        <v>0.8100733406224524</v>
+        <v>0.8182208552569097</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.322064472116108</v>
+        <v>3.171061541565376</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07382227516544687</v>
+        <v>0.0737643095682215</v>
       </c>
       <c r="C24">
-        <v>16.8438561112421</v>
+        <v>16.60676008325751</v>
       </c>
       <c r="D24">
-        <v>22.6278561112421</v>
+        <v>22.67476008325751</v>
       </c>
       <c r="E24">
-        <v>-11.652</v>
+        <v>-11.368</v>
       </c>
       <c r="F24">
-        <v>6.247999999999999</v>
+        <v>6.532</v>
       </c>
       <c r="G24">
         <v>0.464</v>
@@ -3255,28 +3255,28 @@
         <v>1.27</v>
       </c>
       <c r="M24">
-        <v>0.4004968</v>
+        <v>0.4187012000000001</v>
       </c>
       <c r="N24">
-        <v>0.8695031999999998</v>
+        <v>0.8512987999999997</v>
       </c>
       <c r="O24">
-        <v>0.2243318256</v>
+        <v>0.2196350903999999</v>
       </c>
       <c r="P24">
-        <v>0.6451713743999998</v>
+        <v>0.6316637095999997</v>
       </c>
       <c r="Q24">
-        <v>1.6751713744</v>
+        <v>1.6616637096</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08122896303262418</v>
+        <v>0.08159091372496299</v>
       </c>
       <c r="T24">
-        <v>0.8182208552569097</v>
+        <v>0.8265799936481061</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.171061541565376</v>
+        <v>3.03318930062775</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0737643095682215</v>
+        <v>0.07509536797099614</v>
       </c>
       <c r="C25">
-        <v>16.60676008325751</v>
+        <v>15.29251427888324</v>
       </c>
       <c r="D25">
-        <v>22.67476008325751</v>
+        <v>21.64451427888324</v>
       </c>
       <c r="E25">
-        <v>-11.368</v>
+        <v>-11.084</v>
       </c>
       <c r="F25">
-        <v>6.532</v>
+        <v>6.816</v>
       </c>
       <c r="G25">
         <v>0.464</v>
@@ -3337,45 +3337,45 @@
         <v>1.27</v>
       </c>
       <c r="M25">
-        <v>0.4187012000000001</v>
+        <v>0.4900704</v>
       </c>
       <c r="N25">
-        <v>0.8512987999999997</v>
+        <v>0.7799295999999998</v>
       </c>
       <c r="O25">
-        <v>0.2196350903999999</v>
+        <v>0.2012218367999999</v>
       </c>
       <c r="P25">
-        <v>0.6316637095999997</v>
+        <v>0.5787077631999998</v>
       </c>
       <c r="Q25">
-        <v>1.6616637096</v>
+        <v>1.6087077632</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08159091372496299</v>
+        <v>0.08196238943552123</v>
       </c>
       <c r="T25">
-        <v>0.8265799936481061</v>
+        <v>0.8351591093653865</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.03318930062775</v>
+        <v>2.591464410011296</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07509536797099614</v>
+        <v>0.07581872837377077</v>
       </c>
       <c r="C26">
-        <v>15.29251427888324</v>
+        <v>14.48694706352063</v>
       </c>
       <c r="D26">
-        <v>21.64451427888324</v>
+        <v>21.12294706352063</v>
       </c>
       <c r="E26">
-        <v>-11.084</v>
+        <v>-10.8</v>
       </c>
       <c r="F26">
-        <v>6.816</v>
+        <v>7.1</v>
       </c>
       <c r="G26">
         <v>0.464</v>
@@ -3419,45 +3419,45 @@
         <v>1.27</v>
       </c>
       <c r="M26">
-        <v>0.4900704</v>
+        <v>0.53818</v>
       </c>
       <c r="N26">
-        <v>0.7799295999999998</v>
+        <v>0.7318199999999998</v>
       </c>
       <c r="O26">
-        <v>0.2012218367999999</v>
+        <v>0.18880956</v>
       </c>
       <c r="P26">
-        <v>0.5787077631999998</v>
+        <v>0.5430104399999999</v>
       </c>
       <c r="Q26">
-        <v>1.6087077632</v>
+        <v>1.57301044</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08196238943552123</v>
+        <v>0.0823437711650277</v>
       </c>
       <c r="T26">
-        <v>0.8351591093653865</v>
+        <v>0.8439670015017945</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.591464410011296</v>
+        <v>2.359805269612397</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07581872837377077</v>
+        <v>0.07584757677654541</v>
       </c>
       <c r="C27">
-        <v>14.48694706352063</v>
+        <v>14.18266711584939</v>
       </c>
       <c r="D27">
-        <v>21.12294706352063</v>
+        <v>21.10266711584939</v>
       </c>
       <c r="E27">
-        <v>-10.8</v>
+        <v>-10.516</v>
       </c>
       <c r="F27">
-        <v>7.1</v>
+        <v>7.383999999999999</v>
       </c>
       <c r="G27">
         <v>0.464</v>
@@ -3501,28 +3501,28 @@
         <v>1.27</v>
       </c>
       <c r="M27">
-        <v>0.53818</v>
+        <v>0.5597072</v>
       </c>
       <c r="N27">
-        <v>0.7318199999999998</v>
+        <v>0.7102927999999998</v>
       </c>
       <c r="O27">
-        <v>0.18880956</v>
+        <v>0.1832555424</v>
       </c>
       <c r="P27">
-        <v>0.5430104399999999</v>
+        <v>0.5270372575999999</v>
       </c>
       <c r="Q27">
-        <v>1.57301044</v>
+        <v>1.5570372576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0823437711650277</v>
+        <v>0.08273546050884514</v>
       </c>
       <c r="T27">
-        <v>0.8439670015017945</v>
+        <v>0.8530129447770242</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.359805269612397</v>
+        <v>2.269043528473459</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07584757677654541</v>
+        <v>0.07587642517932004</v>
       </c>
       <c r="C28">
-        <v>14.18266711584939</v>
+        <v>13.87842607201033</v>
       </c>
       <c r="D28">
-        <v>21.10266711584939</v>
+        <v>21.08242607201033</v>
       </c>
       <c r="E28">
-        <v>-10.516</v>
+        <v>-10.232</v>
       </c>
       <c r="F28">
-        <v>7.383999999999999</v>
+        <v>7.668</v>
       </c>
       <c r="G28">
         <v>0.464</v>
@@ -3583,28 +3583,28 @@
         <v>1.27</v>
       </c>
       <c r="M28">
-        <v>0.5597072</v>
+        <v>0.5812344</v>
       </c>
       <c r="N28">
-        <v>0.7102927999999998</v>
+        <v>0.6887655999999998</v>
       </c>
       <c r="O28">
-        <v>0.1832555424</v>
+        <v>0.1777015248</v>
       </c>
       <c r="P28">
-        <v>0.5270372575999999</v>
+        <v>0.5110640751999997</v>
       </c>
       <c r="Q28">
-        <v>1.5570372576</v>
+        <v>1.5410640752</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08273546050884514</v>
+        <v>0.0831378810675617</v>
       </c>
       <c r="T28">
-        <v>0.8530129447770242</v>
+        <v>0.8623067221145891</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.269043528473459</v>
+        <v>2.185004879270738</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07587642517932004</v>
+        <v>0.07590527358209467</v>
       </c>
       <c r="C29">
-        <v>13.87842607201033</v>
+        <v>13.57422382016454</v>
       </c>
       <c r="D29">
-        <v>21.08242607201033</v>
+        <v>21.06222382016454</v>
       </c>
       <c r="E29">
-        <v>-10.232</v>
+        <v>-9.947999999999999</v>
       </c>
       <c r="F29">
-        <v>7.668</v>
+        <v>7.952</v>
       </c>
       <c r="G29">
         <v>0.464</v>
@@ -3665,28 +3665,28 @@
         <v>1.27</v>
       </c>
       <c r="M29">
-        <v>0.5812344</v>
+        <v>0.6027616</v>
       </c>
       <c r="N29">
-        <v>0.6887655999999998</v>
+        <v>0.6672383999999998</v>
       </c>
       <c r="O29">
-        <v>0.1777015248</v>
+        <v>0.1721475071999999</v>
       </c>
       <c r="P29">
-        <v>0.5110640751999997</v>
+        <v>0.4950908927999998</v>
       </c>
       <c r="Q29">
-        <v>1.5410640752</v>
+        <v>1.5250908928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0831378810675617</v>
+        <v>0.08355147997513149</v>
       </c>
       <c r="T29">
-        <v>0.8623067221145891</v>
+        <v>0.871858659933753</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.185004879270738</v>
+        <v>2.106968990725354</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07590527358209467</v>
+        <v>0.0759341219848693</v>
       </c>
       <c r="C30">
-        <v>13.57422382016454</v>
+        <v>13.27006024890142</v>
       </c>
       <c r="D30">
-        <v>21.06222382016454</v>
+        <v>21.04206024890142</v>
       </c>
       <c r="E30">
-        <v>-9.947999999999999</v>
+        <v>-9.663999999999998</v>
       </c>
       <c r="F30">
-        <v>7.952</v>
+        <v>8.236000000000001</v>
       </c>
       <c r="G30">
         <v>0.464</v>
@@ -3747,28 +3747,28 @@
         <v>1.27</v>
       </c>
       <c r="M30">
-        <v>0.6027616</v>
+        <v>0.6242888000000001</v>
       </c>
       <c r="N30">
-        <v>0.6672383999999998</v>
+        <v>0.6457111999999997</v>
       </c>
       <c r="O30">
-        <v>0.1721475071999999</v>
+        <v>0.1665934895999999</v>
       </c>
       <c r="P30">
-        <v>0.4950908927999998</v>
+        <v>0.4791177103999998</v>
       </c>
       <c r="Q30">
-        <v>1.5250908928</v>
+        <v>1.5091177104</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08355147997513149</v>
+        <v>0.08397672955615396</v>
       </c>
       <c r="T30">
-        <v>0.871858659933753</v>
+        <v>0.8816796664238791</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.106968990725354</v>
+        <v>2.034314887596894</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0759341219848693</v>
+        <v>0.07912389038764395</v>
       </c>
       <c r="C31">
-        <v>13.27006024890142</v>
+        <v>10.97191069641961</v>
       </c>
       <c r="D31">
-        <v>21.04206024890142</v>
+        <v>19.02791069641961</v>
       </c>
       <c r="E31">
-        <v>-9.664</v>
+        <v>-9.379999999999999</v>
       </c>
       <c r="F31">
-        <v>8.235999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G31">
         <v>0.464</v>
@@ -3829,45 +3829,45 @@
         <v>1.27</v>
       </c>
       <c r="M31">
-        <v>0.6242888</v>
+        <v>0.7667999999999999</v>
       </c>
       <c r="N31">
-        <v>0.6457111999999998</v>
+        <v>0.5031999999999999</v>
       </c>
       <c r="O31">
-        <v>0.1665934895999999</v>
+        <v>0.1298256</v>
       </c>
       <c r="P31">
-        <v>0.4791177103999998</v>
+        <v>0.3733743999999999</v>
       </c>
       <c r="Q31">
-        <v>1.5091177104</v>
+        <v>1.4033744</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08397672955615396</v>
+        <v>0.08441412912520564</v>
       </c>
       <c r="T31">
-        <v>0.8816796664238791</v>
+        <v>0.8917812730994376</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.034314887596894</v>
+        <v>1.656233698487219</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07912389038764395</v>
+        <v>0.07925810279041857</v>
       </c>
       <c r="C32">
-        <v>10.97191069641961</v>
+        <v>10.61158294913685</v>
       </c>
       <c r="D32">
-        <v>19.02791069641961</v>
+        <v>18.95158294913685</v>
       </c>
       <c r="E32">
-        <v>-9.379999999999999</v>
+        <v>-9.095999999999998</v>
       </c>
       <c r="F32">
-        <v>8.52</v>
+        <v>8.804</v>
       </c>
       <c r="G32">
         <v>0.464</v>
@@ -3911,28 +3911,28 @@
         <v>1.27</v>
       </c>
       <c r="M32">
-        <v>0.7667999999999999</v>
+        <v>0.79236</v>
       </c>
       <c r="N32">
-        <v>0.5031999999999999</v>
+        <v>0.4776399999999998</v>
       </c>
       <c r="O32">
-        <v>0.1298256</v>
+        <v>0.12323112</v>
       </c>
       <c r="P32">
-        <v>0.3733743999999999</v>
+        <v>0.3544088799999999</v>
       </c>
       <c r="Q32">
-        <v>1.4033744</v>
+        <v>1.38440888</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08441412912520564</v>
+        <v>0.08486420694263563</v>
       </c>
       <c r="T32">
-        <v>0.8917812730994376</v>
+        <v>0.9021756799684905</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.656233698487219</v>
+        <v>1.602806804987632</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07925810279041857</v>
+        <v>0.07939231519319322</v>
       </c>
       <c r="C33">
-        <v>10.61158294913685</v>
+        <v>10.25186511101351</v>
       </c>
       <c r="D33">
-        <v>18.95158294913685</v>
+        <v>18.87586511101351</v>
       </c>
       <c r="E33">
-        <v>-9.095999999999998</v>
+        <v>-8.811999999999999</v>
       </c>
       <c r="F33">
-        <v>8.804</v>
+        <v>9.087999999999999</v>
       </c>
       <c r="G33">
         <v>0.464</v>
@@ -3993,28 +3993,28 @@
         <v>1.27</v>
       </c>
       <c r="M33">
-        <v>0.79236</v>
+        <v>0.8179199999999999</v>
       </c>
       <c r="N33">
-        <v>0.4776399999999998</v>
+        <v>0.4520799999999999</v>
       </c>
       <c r="O33">
-        <v>0.12323112</v>
+        <v>0.11663664</v>
       </c>
       <c r="P33">
-        <v>0.3544088799999999</v>
+        <v>0.33544336</v>
       </c>
       <c r="Q33">
-        <v>1.38440888</v>
+        <v>1.36544336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08486420694263563</v>
+        <v>0.0853275223429312</v>
       </c>
       <c r="T33">
-        <v>0.9021756799684905</v>
+        <v>0.9128758046866331</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.602806804987632</v>
+        <v>1.552719092331768</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07939231519319322</v>
+        <v>0.07952652759596784</v>
       </c>
       <c r="C34">
-        <v>10.25186511101351</v>
+        <v>9.892749900774614</v>
       </c>
       <c r="D34">
-        <v>18.87586511101351</v>
+        <v>18.80074990077462</v>
       </c>
       <c r="E34">
-        <v>-8.811999999999999</v>
+        <v>-8.527999999999999</v>
       </c>
       <c r="F34">
-        <v>9.087999999999999</v>
+        <v>9.372</v>
       </c>
       <c r="G34">
         <v>0.464</v>
@@ -4075,28 +4075,28 @@
         <v>1.27</v>
       </c>
       <c r="M34">
-        <v>0.8179199999999999</v>
+        <v>0.84348</v>
       </c>
       <c r="N34">
-        <v>0.4520799999999999</v>
+        <v>0.4265199999999998</v>
       </c>
       <c r="O34">
-        <v>0.11663664</v>
+        <v>0.1100421599999999</v>
       </c>
       <c r="P34">
-        <v>0.33544336</v>
+        <v>0.3164778399999998</v>
       </c>
       <c r="Q34">
-        <v>1.36544336</v>
+        <v>1.34647784</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0853275223429312</v>
+        <v>0.08580466805368336</v>
       </c>
       <c r="T34">
-        <v>0.9128758046866331</v>
+        <v>0.9238953361127799</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.552719092331768</v>
+        <v>1.505666998624745</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07952652759596784</v>
+        <v>0.09559764014123825</v>
       </c>
       <c r="C35">
-        <v>9.892749900774614</v>
+        <v>3.541214034941172</v>
       </c>
       <c r="D35">
-        <v>18.80074990077462</v>
+        <v>12.73321403494117</v>
       </c>
       <c r="E35">
-        <v>-8.527999999999999</v>
+        <v>-8.243999999999998</v>
       </c>
       <c r="F35">
-        <v>9.372</v>
+        <v>9.656000000000001</v>
       </c>
       <c r="G35">
         <v>0.464</v>
@@ -4157,45 +4157,45 @@
         <v>1.27</v>
       </c>
       <c r="M35">
-        <v>0.84348</v>
+        <v>1.4175008</v>
       </c>
       <c r="N35">
-        <v>0.4265199999999998</v>
+        <v>-0.1475008000000004</v>
       </c>
       <c r="O35">
-        <v>0.1100421599999999</v>
+        <v>-0.03805520640000011</v>
       </c>
       <c r="P35">
-        <v>0.3164778399999998</v>
+        <v>-0.1094455936000003</v>
       </c>
       <c r="Q35">
-        <v>1.34647784</v>
+        <v>0.9205544063999997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08580466805368336</v>
+        <v>0.08670146073469731</v>
       </c>
       <c r="T35">
-        <v>0.9238953361127799</v>
+        <v>0.9446064834803074</v>
       </c>
       <c r="U35">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.258</v>
+        <v>0.2311533086965453</v>
       </c>
       <c r="W35">
-        <v>0.06677999999999999</v>
+        <v>0.1128666942833472</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.505666998624745</v>
+        <v>0.8959430569633537</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09559764014123825</v>
+        <v>0.09660764014123824</v>
       </c>
       <c r="C36">
-        <v>3.541214034941172</v>
+        <v>3.004091745861421</v>
       </c>
       <c r="D36">
-        <v>12.73321403494117</v>
+        <v>12.48009174586142</v>
       </c>
       <c r="E36">
-        <v>-8.243999999999998</v>
+        <v>-7.959999999999997</v>
       </c>
       <c r="F36">
-        <v>9.656000000000001</v>
+        <v>9.940000000000001</v>
       </c>
       <c r="G36">
         <v>0.464</v>
@@ -4239,37 +4239,37 @@
         <v>1.27</v>
       </c>
       <c r="M36">
-        <v>1.4175008</v>
+        <v>1.459192</v>
       </c>
       <c r="N36">
-        <v>-0.1475008000000004</v>
+        <v>-0.1891920000000005</v>
       </c>
       <c r="O36">
-        <v>-0.03805520640000011</v>
+        <v>-0.04881153600000012</v>
       </c>
       <c r="P36">
-        <v>-0.1094455936000003</v>
+        <v>-0.1403804640000003</v>
       </c>
       <c r="Q36">
-        <v>0.9205544063999997</v>
+        <v>0.8896195359999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08670146073469731</v>
+        <v>0.08733071397676956</v>
       </c>
       <c r="T36">
-        <v>0.9446064834803074</v>
+        <v>0.9591388909184658</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2311533086965453</v>
+        <v>0.2245489284480726</v>
       </c>
       <c r="W36">
-        <v>0.1128666942833472</v>
+        <v>0.113836217303823</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8959430569633537</v>
+        <v>0.8703446839072579</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09660764014123824</v>
+        <v>0.09761764014123825</v>
       </c>
       <c r="C37">
-        <v>3.004091745861421</v>
+        <v>2.47683688846222</v>
       </c>
       <c r="D37">
-        <v>12.48009174586142</v>
+        <v>12.23683688846222</v>
       </c>
       <c r="E37">
-        <v>-7.959999999999997</v>
+        <v>-7.675999999999998</v>
       </c>
       <c r="F37">
-        <v>9.940000000000001</v>
+        <v>10.224</v>
       </c>
       <c r="G37">
         <v>0.464</v>
@@ -4321,37 +4321,37 @@
         <v>1.27</v>
       </c>
       <c r="M37">
-        <v>1.459192</v>
+        <v>1.5008832</v>
       </c>
       <c r="N37">
-        <v>-0.1891920000000005</v>
+        <v>-0.2308832000000003</v>
       </c>
       <c r="O37">
-        <v>-0.04881153600000012</v>
+        <v>-0.05956786560000008</v>
       </c>
       <c r="P37">
-        <v>-0.1403804640000003</v>
+        <v>-0.1713153344000002</v>
       </c>
       <c r="Q37">
-        <v>0.8896195359999997</v>
+        <v>0.8586846655999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08733071397676956</v>
+        <v>0.08797963138265659</v>
       </c>
       <c r="T37">
-        <v>0.9591388909184658</v>
+        <v>0.974125436089067</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2245489284480726</v>
+        <v>0.2183114582134039</v>
       </c>
       <c r="W37">
-        <v>0.113836217303823</v>
+        <v>0.1147518779342723</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8703446839072579</v>
+        <v>0.846168442687612</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09761764014123825</v>
+        <v>0.09862764014123826</v>
       </c>
       <c r="C38">
-        <v>2.476836888462222</v>
+        <v>1.958883502993858</v>
       </c>
       <c r="D38">
-        <v>12.23683688846222</v>
+        <v>12.00288350299386</v>
       </c>
       <c r="E38">
-        <v>-7.676</v>
+        <v>-7.391999999999999</v>
       </c>
       <c r="F38">
-        <v>10.224</v>
+        <v>10.508</v>
       </c>
       <c r="G38">
         <v>0.464</v>
@@ -4403,37 +4403,37 @@
         <v>1.27</v>
       </c>
       <c r="M38">
-        <v>1.5008832</v>
+        <v>1.5425744</v>
       </c>
       <c r="N38">
-        <v>-0.2308832000000001</v>
+        <v>-0.2725744000000003</v>
       </c>
       <c r="O38">
-        <v>-0.05956786560000002</v>
+        <v>-0.07032419520000009</v>
       </c>
       <c r="P38">
-        <v>-0.1713153344</v>
+        <v>-0.2022502048000002</v>
       </c>
       <c r="Q38">
-        <v>0.8586846656</v>
+        <v>0.8277497951999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08797963138265659</v>
+        <v>0.08864914934111146</v>
       </c>
       <c r="T38">
-        <v>0.9741254360890669</v>
+        <v>0.9895877445984173</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2183114582134039</v>
+        <v>0.2124111485319606</v>
       </c>
       <c r="W38">
-        <v>0.1147518779342723</v>
+        <v>0.1156180433955082</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8461684426876122</v>
+        <v>0.8232990253176765</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09862764014123826</v>
+        <v>0.09963764014123826</v>
       </c>
       <c r="C39">
-        <v>1.958883502993858</v>
+        <v>1.449708099573122</v>
       </c>
       <c r="D39">
-        <v>12.00288350299386</v>
+        <v>11.77770809957312</v>
       </c>
       <c r="E39">
-        <v>-7.391999999999999</v>
+        <v>-7.107999999999999</v>
       </c>
       <c r="F39">
-        <v>10.508</v>
+        <v>10.792</v>
       </c>
       <c r="G39">
         <v>0.464</v>
@@ -4485,37 +4485,37 @@
         <v>1.27</v>
       </c>
       <c r="M39">
-        <v>1.5425744</v>
+        <v>1.5842656</v>
       </c>
       <c r="N39">
-        <v>-0.2725744000000003</v>
+        <v>-0.3142656000000004</v>
       </c>
       <c r="O39">
-        <v>-0.07032419520000009</v>
+        <v>-0.08108052480000009</v>
       </c>
       <c r="P39">
-        <v>-0.2022502048000002</v>
+        <v>-0.2331850752000003</v>
       </c>
       <c r="Q39">
-        <v>0.8277497951999998</v>
+        <v>0.7968149247999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08864914934111146</v>
+        <v>0.08934026465306487</v>
       </c>
       <c r="T39">
-        <v>0.9895877445984173</v>
+        <v>1.00554883725323</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2124111485319606</v>
+        <v>0.20682138146533</v>
       </c>
       <c r="W39">
-        <v>0.1156180433955082</v>
+        <v>0.1164386212008896</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8232990253176765</v>
+        <v>0.8016332614935271</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09963764014123826</v>
+        <v>0.1223268529293521</v>
       </c>
       <c r="C40">
-        <v>1.449708099573122</v>
+        <v>-2.32622858668006</v>
       </c>
       <c r="D40">
-        <v>11.77770809957312</v>
+        <v>8.28577141331994</v>
       </c>
       <c r="E40">
-        <v>-7.107999999999999</v>
+        <v>-6.823999999999998</v>
       </c>
       <c r="F40">
-        <v>10.792</v>
+        <v>11.076</v>
       </c>
       <c r="G40">
         <v>0.464</v>
@@ -4567,45 +4567,45 @@
         <v>1.27</v>
       </c>
       <c r="M40">
-        <v>1.5842656</v>
+        <v>2.2240608</v>
       </c>
       <c r="N40">
-        <v>-0.3142656000000004</v>
+        <v>-0.9540608000000004</v>
       </c>
       <c r="O40">
-        <v>-0.08108052480000009</v>
+        <v>-0.2461476864000001</v>
       </c>
       <c r="P40">
-        <v>-0.2331850752000003</v>
+        <v>-0.7079131136000003</v>
       </c>
       <c r="Q40">
-        <v>0.7968149247999998</v>
+        <v>0.3220868863999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08934026465306487</v>
+        <v>0.09106914241477709</v>
       </c>
       <c r="T40">
-        <v>1.00554883725323</v>
+        <v>1.04547673013342</v>
       </c>
       <c r="U40">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.20682138146533</v>
+        <v>0.1473251090977369</v>
       </c>
       <c r="W40">
-        <v>0.1164386212008896</v>
+        <v>0.1712171180931744</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.8016332614935271</v>
+        <v>0.5710275546423909</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1223268529293521</v>
+        <v>0.123876852929352</v>
       </c>
       <c r="C41">
-        <v>-2.32622858668006</v>
+        <v>-2.774719664493695</v>
       </c>
       <c r="D41">
-        <v>8.28577141331994</v>
+        <v>8.121280335506304</v>
       </c>
       <c r="E41">
-        <v>-6.823999999999998</v>
+        <v>-6.539999999999999</v>
       </c>
       <c r="F41">
-        <v>11.076</v>
+        <v>11.36</v>
       </c>
       <c r="G41">
         <v>0.464</v>
@@ -4649,37 +4649,37 @@
         <v>1.27</v>
       </c>
       <c r="M41">
-        <v>2.2240608</v>
+        <v>2.281088</v>
       </c>
       <c r="N41">
-        <v>-0.9540608000000004</v>
+        <v>-1.011088</v>
       </c>
       <c r="O41">
-        <v>-0.2461476864000001</v>
+        <v>-0.2608607040000001</v>
       </c>
       <c r="P41">
-        <v>-0.7079131136000003</v>
+        <v>-0.7502272960000002</v>
       </c>
       <c r="Q41">
-        <v>0.3220868863999997</v>
+        <v>0.2797727039999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09106914241477709</v>
+        <v>0.09182362812169004</v>
       </c>
       <c r="T41">
-        <v>1.04547673013342</v>
+        <v>1.062901342302311</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1473251090977369</v>
+        <v>0.1436419813702934</v>
       </c>
       <c r="W41">
-        <v>0.1712171180931744</v>
+        <v>0.1719566901408451</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5710275546423909</v>
+        <v>0.5567518657763312</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.123876852929352</v>
+        <v>0.1254268529293521</v>
       </c>
       <c r="C42">
-        <v>-2.774719664493695</v>
+        <v>-3.216806843089131</v>
       </c>
       <c r="D42">
-        <v>8.121280335506304</v>
+        <v>7.96319315691087</v>
       </c>
       <c r="E42">
-        <v>-6.539999999999999</v>
+        <v>-6.255999999999998</v>
       </c>
       <c r="F42">
-        <v>11.36</v>
+        <v>11.644</v>
       </c>
       <c r="G42">
         <v>0.464</v>
@@ -4731,37 +4731,37 @@
         <v>1.27</v>
       </c>
       <c r="M42">
-        <v>2.281088</v>
+        <v>2.3381152</v>
       </c>
       <c r="N42">
-        <v>-1.011088</v>
+        <v>-1.0681152</v>
       </c>
       <c r="O42">
-        <v>-0.2608607040000001</v>
+        <v>-0.2755737216000002</v>
       </c>
       <c r="P42">
-        <v>-0.7502272960000002</v>
+        <v>-0.7925414784000003</v>
       </c>
       <c r="Q42">
-        <v>0.2797727039999999</v>
+        <v>0.2374585215999997</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09182362812169004</v>
+        <v>0.09260368961527801</v>
       </c>
       <c r="T42">
-        <v>1.062901342302311</v>
+        <v>1.080916619290485</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1436419813702934</v>
+        <v>0.1401385184100424</v>
       </c>
       <c r="W42">
-        <v>0.1719566901408451</v>
+        <v>0.1726601855032635</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5567518657763312</v>
+        <v>0.5431725519769084</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1254268529293521</v>
+        <v>0.1269768529293521</v>
       </c>
       <c r="C43">
-        <v>-3.216806843089131</v>
+        <v>-3.652856952791634</v>
       </c>
       <c r="D43">
-        <v>7.96319315691087</v>
+        <v>7.811143047208366</v>
       </c>
       <c r="E43">
-        <v>-6.255999999999998</v>
+        <v>-5.971999999999998</v>
       </c>
       <c r="F43">
-        <v>11.644</v>
+        <v>11.928</v>
       </c>
       <c r="G43">
         <v>0.464</v>
@@ -4813,37 +4813,37 @@
         <v>1.27</v>
       </c>
       <c r="M43">
-        <v>2.3381152</v>
+        <v>2.3951424</v>
       </c>
       <c r="N43">
-        <v>-1.0681152</v>
+        <v>-1.1251424</v>
       </c>
       <c r="O43">
-        <v>-0.2755737216000002</v>
+        <v>-0.2902867392000001</v>
       </c>
       <c r="P43">
-        <v>-0.7925414784000003</v>
+        <v>-0.8348556608000002</v>
       </c>
       <c r="Q43">
-        <v>0.2374585215999997</v>
+        <v>0.1951443391999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09260368961527801</v>
+        <v>0.09341064978105866</v>
       </c>
       <c r="T43">
-        <v>1.080916619290485</v>
+        <v>1.099553112726528</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1401385184100424</v>
+        <v>0.1368018870193271</v>
       </c>
       <c r="W43">
-        <v>0.1726601855032635</v>
+        <v>0.1733301810865191</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5431725519769084</v>
+        <v>0.5302398721679344</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.126976852929352</v>
+        <v>0.1285268529293521</v>
       </c>
       <c r="C44">
-        <v>-3.652856952791629</v>
+        <v>-4.083209331668082</v>
       </c>
       <c r="D44">
-        <v>7.81114304720837</v>
+        <v>7.664790668331918</v>
       </c>
       <c r="E44">
-        <v>-5.972</v>
+        <v>-5.687999999999999</v>
       </c>
       <c r="F44">
-        <v>11.928</v>
+        <v>12.212</v>
       </c>
       <c r="G44">
         <v>0.464</v>
@@ -4895,37 +4895,37 @@
         <v>1.27</v>
       </c>
       <c r="M44">
-        <v>2.3951424</v>
+        <v>2.4521696</v>
       </c>
       <c r="N44">
-        <v>-1.1251424</v>
+        <v>-1.1821696</v>
       </c>
       <c r="O44">
-        <v>-0.2902867392</v>
+        <v>-0.3049997568</v>
       </c>
       <c r="P44">
-        <v>-0.8348556608</v>
+        <v>-0.8771698432000001</v>
       </c>
       <c r="Q44">
-        <v>0.1951443392000001</v>
+        <v>0.1528301567999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09341064978105865</v>
+        <v>0.09424592433862108</v>
       </c>
       <c r="T44">
-        <v>1.099553112726528</v>
+        <v>1.118843518212958</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1368018870193271</v>
+        <v>0.1336204477863195</v>
       </c>
       <c r="W44">
-        <v>0.1733301810865191</v>
+        <v>0.1739690140845071</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5302398721679346</v>
+        <v>0.5179087123500756</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1285268529293521</v>
+        <v>0.1300768529293521</v>
       </c>
       <c r="C45">
-        <v>-4.083209331668082</v>
+        <v>-4.508178353682627</v>
       </c>
       <c r="D45">
-        <v>7.664790668331918</v>
+        <v>7.523821646317371</v>
       </c>
       <c r="E45">
-        <v>-5.687999999999999</v>
+        <v>-5.404</v>
       </c>
       <c r="F45">
-        <v>12.212</v>
+        <v>12.496</v>
       </c>
       <c r="G45">
         <v>0.464</v>
@@ -4977,37 +4977,37 @@
         <v>1.27</v>
       </c>
       <c r="M45">
-        <v>2.4521696</v>
+        <v>2.5091968</v>
       </c>
       <c r="N45">
-        <v>-1.1821696</v>
+        <v>-1.2391968</v>
       </c>
       <c r="O45">
-        <v>-0.3049997568</v>
+        <v>-0.3197127744</v>
       </c>
       <c r="P45">
-        <v>-0.8771698432000001</v>
+        <v>-0.9194840256</v>
       </c>
       <c r="Q45">
-        <v>0.1528301567999999</v>
+        <v>0.1105159744</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09424592433862108</v>
+        <v>0.09511103013038219</v>
       </c>
       <c r="T45">
-        <v>1.118843518212958</v>
+        <v>1.138822866752476</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1336204477863195</v>
+        <v>0.1305836194275395</v>
       </c>
       <c r="W45">
-        <v>0.1739690140845071</v>
+        <v>0.1745788092189501</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5179087123500756</v>
+        <v>0.5061380597966647</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1300768529293521</v>
+        <v>0.147626712768617</v>
       </c>
       <c r="C46">
-        <v>-4.508178353682627</v>
+        <v>-6.08891092766387</v>
       </c>
       <c r="D46">
-        <v>7.523821646317371</v>
+        <v>6.227089072336129</v>
       </c>
       <c r="E46">
-        <v>-5.404</v>
+        <v>-5.119999999999999</v>
       </c>
       <c r="F46">
-        <v>12.496</v>
+        <v>12.78</v>
       </c>
       <c r="G46">
         <v>0.464</v>
@@ -5059,45 +5059,45 @@
         <v>1.27</v>
       </c>
       <c r="M46">
-        <v>2.5091968</v>
+        <v>3.013524</v>
       </c>
       <c r="N46">
-        <v>-1.2391968</v>
+        <v>-1.743524</v>
       </c>
       <c r="O46">
-        <v>-0.3197127744</v>
+        <v>-0.449829192</v>
       </c>
       <c r="P46">
-        <v>-0.9194840256</v>
+        <v>-1.293694808</v>
       </c>
       <c r="Q46">
-        <v>0.1105159744</v>
+        <v>-0.2636948080000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09511103013038219</v>
+        <v>0.09646188493141634</v>
       </c>
       <c r="T46">
-        <v>1.138822866752476</v>
+        <v>1.170020437215158</v>
       </c>
       <c r="U46">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1305836194275395</v>
+        <v>0.1087298458548862</v>
       </c>
       <c r="W46">
-        <v>0.1745788092189501</v>
+        <v>0.2101615023474178</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5061380597966647</v>
+        <v>0.4214335110654502</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.147626712768617</v>
+        <v>0.149526712768617</v>
       </c>
       <c r="C47">
-        <v>-6.08891092766387</v>
+        <v>-6.48697478760544</v>
       </c>
       <c r="D47">
-        <v>6.227089072336129</v>
+        <v>6.11302521239456</v>
       </c>
       <c r="E47">
-        <v>-5.119999999999999</v>
+        <v>-4.835999999999999</v>
       </c>
       <c r="F47">
-        <v>12.78</v>
+        <v>13.064</v>
       </c>
       <c r="G47">
         <v>0.464</v>
@@ -5141,37 +5141,37 @@
         <v>1.27</v>
       </c>
       <c r="M47">
-        <v>3.013524</v>
+        <v>3.0804912</v>
       </c>
       <c r="N47">
-        <v>-1.743524</v>
+        <v>-1.8104912</v>
       </c>
       <c r="O47">
-        <v>-0.449829192</v>
+        <v>-0.4671067296</v>
       </c>
       <c r="P47">
-        <v>-1.293694808</v>
+        <v>-1.3433844704</v>
       </c>
       <c r="Q47">
-        <v>-0.2636948080000001</v>
+        <v>-0.3133844704000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09646188493141634</v>
+        <v>0.09740006798570183</v>
       </c>
       <c r="T47">
-        <v>1.170020437215158</v>
+        <v>1.191687482348772</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1087298458548862</v>
+        <v>0.106366153553693</v>
       </c>
       <c r="W47">
-        <v>0.2101615023474178</v>
+        <v>0.2107188609920392</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4214335110654502</v>
+        <v>0.4122719129988099</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.149526712768617</v>
+        <v>0.151426712768617</v>
       </c>
       <c r="C48">
-        <v>-6.48697478760544</v>
+        <v>-6.880935114866525</v>
       </c>
       <c r="D48">
-        <v>6.11302521239456</v>
+        <v>6.003064885133475</v>
       </c>
       <c r="E48">
-        <v>-4.835999999999999</v>
+        <v>-4.551999999999998</v>
       </c>
       <c r="F48">
-        <v>13.064</v>
+        <v>13.348</v>
       </c>
       <c r="G48">
         <v>0.464</v>
@@ -5223,37 +5223,37 @@
         <v>1.27</v>
       </c>
       <c r="M48">
-        <v>3.0804912</v>
+        <v>3.1474584</v>
       </c>
       <c r="N48">
-        <v>-1.8104912</v>
+        <v>-1.8774584</v>
       </c>
       <c r="O48">
-        <v>-0.4671067296</v>
+        <v>-0.4843842672000001</v>
       </c>
       <c r="P48">
-        <v>-1.3433844704</v>
+        <v>-1.3930741328</v>
       </c>
       <c r="Q48">
-        <v>-0.3133844704000002</v>
+        <v>-0.3630741328000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09740006798570183</v>
+        <v>0.09837365417411131</v>
       </c>
       <c r="T48">
-        <v>1.191687482348772</v>
+        <v>1.214172151827051</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.106366153553693</v>
+        <v>0.1041030439036144</v>
       </c>
       <c r="W48">
-        <v>0.2107188609920392</v>
+        <v>0.2112525022475278</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4122719129988099</v>
+        <v>0.403500170169048</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.151426712768617</v>
+        <v>0.153326712768617</v>
       </c>
       <c r="C49">
-        <v>-6.880935114866525</v>
+        <v>-7.27100943805631</v>
       </c>
       <c r="D49">
-        <v>6.003064885133475</v>
+        <v>5.89699056194369</v>
       </c>
       <c r="E49">
-        <v>-4.551999999999998</v>
+        <v>-4.267999999999999</v>
       </c>
       <c r="F49">
-        <v>13.348</v>
+        <v>13.632</v>
       </c>
       <c r="G49">
         <v>0.464</v>
@@ -5305,37 +5305,37 @@
         <v>1.27</v>
       </c>
       <c r="M49">
-        <v>3.1474584</v>
+        <v>3.2144256</v>
       </c>
       <c r="N49">
-        <v>-1.8774584</v>
+        <v>-1.9444256</v>
       </c>
       <c r="O49">
-        <v>-0.4843842672000001</v>
+        <v>-0.5016618048000001</v>
       </c>
       <c r="P49">
-        <v>-1.3930741328</v>
+        <v>-1.4427637952</v>
       </c>
       <c r="Q49">
-        <v>-0.3630741328000002</v>
+        <v>-0.4127637952000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09837365417411131</v>
+        <v>0.0993846859851519</v>
       </c>
       <c r="T49">
-        <v>1.214172151827051</v>
+        <v>1.237521616285264</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1041030439036144</v>
+        <v>0.1019342304889558</v>
       </c>
       <c r="W49">
-        <v>0.2112525022475278</v>
+        <v>0.2117639084507042</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.403500170169048</v>
+        <v>0.3950939166238595</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.153326712768617</v>
+        <v>0.155226712768617</v>
       </c>
       <c r="C50">
-        <v>-7.27100943805631</v>
+        <v>-7.657400177796288</v>
       </c>
       <c r="D50">
-        <v>5.89699056194369</v>
+        <v>5.79459982220371</v>
       </c>
       <c r="E50">
-        <v>-4.267999999999999</v>
+        <v>-3.984</v>
       </c>
       <c r="F50">
-        <v>13.632</v>
+        <v>13.916</v>
       </c>
       <c r="G50">
         <v>0.464</v>
@@ -5387,37 +5387,37 @@
         <v>1.27</v>
       </c>
       <c r="M50">
-        <v>3.2144256</v>
+        <v>3.2813928</v>
       </c>
       <c r="N50">
-        <v>-1.9444256</v>
+        <v>-2.0113928</v>
       </c>
       <c r="O50">
-        <v>-0.5016618048000001</v>
+        <v>-0.5189393424000001</v>
       </c>
       <c r="P50">
-        <v>-1.4427637952</v>
+        <v>-1.4924534576</v>
       </c>
       <c r="Q50">
-        <v>-0.4127637952000003</v>
+        <v>-0.4624534576000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0993846859851519</v>
+        <v>0.1004353661025078</v>
       </c>
       <c r="T50">
-        <v>1.237521616285264</v>
+        <v>1.261786746016347</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1019342304889558</v>
+        <v>0.09985394007081383</v>
       </c>
       <c r="W50">
-        <v>0.2117639084507042</v>
+        <v>0.2122544409313021</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3950939166238595</v>
+        <v>0.3870307754682706</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.155226712768617</v>
+        <v>0.157126712768617</v>
       </c>
       <c r="C51">
-        <v>-7.657400177796288</v>
+        <v>-8.040295935951566</v>
       </c>
       <c r="D51">
-        <v>5.79459982220371</v>
+        <v>5.695704064048434</v>
       </c>
       <c r="E51">
-        <v>-3.984</v>
+        <v>-3.699999999999999</v>
       </c>
       <c r="F51">
-        <v>13.916</v>
+        <v>14.2</v>
       </c>
       <c r="G51">
         <v>0.464</v>
@@ -5469,37 +5469,37 @@
         <v>1.27</v>
       </c>
       <c r="M51">
-        <v>3.2813928</v>
+        <v>3.34836</v>
       </c>
       <c r="N51">
-        <v>-2.0113928</v>
+        <v>-2.07836</v>
       </c>
       <c r="O51">
-        <v>-0.5189393424000001</v>
+        <v>-0.53621688</v>
       </c>
       <c r="P51">
-        <v>-1.4924534576</v>
+        <v>-1.54214312</v>
       </c>
       <c r="Q51">
-        <v>-0.4624534576000003</v>
+        <v>-0.51214312</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1004353661025078</v>
+        <v>0.101528073424558</v>
       </c>
       <c r="T51">
-        <v>1.261786746016347</v>
+        <v>1.287022480936674</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.09985394007081383</v>
+        <v>0.09785686126939755</v>
       </c>
       <c r="W51">
-        <v>0.2122544409313021</v>
+        <v>0.2127253521126761</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3870307754682706</v>
+        <v>0.3792901599589052</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.157126712768617</v>
+        <v>0.159026712768617</v>
       </c>
       <c r="C52">
-        <v>-8.040295935951566</v>
+        <v>-8.419872655058539</v>
       </c>
       <c r="D52">
-        <v>5.695704064048434</v>
+        <v>5.600127344941461</v>
       </c>
       <c r="E52">
-        <v>-3.699999999999999</v>
+        <v>-3.415999999999999</v>
       </c>
       <c r="F52">
-        <v>14.2</v>
+        <v>14.484</v>
       </c>
       <c r="G52">
         <v>0.464</v>
@@ -5551,37 +5551,37 @@
         <v>1.27</v>
       </c>
       <c r="M52">
-        <v>3.34836</v>
+        <v>3.4153272</v>
       </c>
       <c r="N52">
-        <v>-2.07836</v>
+        <v>-2.145327200000001</v>
       </c>
       <c r="O52">
-        <v>-0.53621688</v>
+        <v>-0.5534944176000002</v>
       </c>
       <c r="P52">
-        <v>-1.54214312</v>
+        <v>-1.5918327824</v>
       </c>
       <c r="Q52">
-        <v>-0.51214312</v>
+        <v>-0.5618327824000005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.101528073424558</v>
+        <v>0.1026653810454673</v>
       </c>
       <c r="T52">
-        <v>1.287022480936674</v>
+        <v>1.313288245853749</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.09785686126939755</v>
+        <v>0.09593809928372307</v>
       </c>
       <c r="W52">
-        <v>0.2127253521126761</v>
+        <v>0.2131777961888981</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3792901599589052</v>
+        <v>0.3718530979989266</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.159026712768617</v>
+        <v>0.160926712768617</v>
       </c>
       <c r="C53">
-        <v>-8.419872655058539</v>
+        <v>-8.796294662944524</v>
       </c>
       <c r="D53">
-        <v>5.600127344941461</v>
+        <v>5.507705337055475</v>
       </c>
       <c r="E53">
-        <v>-3.415999999999999</v>
+        <v>-3.132</v>
       </c>
       <c r="F53">
-        <v>14.484</v>
+        <v>14.768</v>
       </c>
       <c r="G53">
         <v>0.464</v>
@@ -5633,37 +5633,37 @@
         <v>1.27</v>
       </c>
       <c r="M53">
-        <v>3.4153272</v>
+        <v>3.4822944</v>
       </c>
       <c r="N53">
-        <v>-2.145327200000001</v>
+        <v>-2.2122944</v>
       </c>
       <c r="O53">
-        <v>-0.5534944176000002</v>
+        <v>-0.5707719552000001</v>
       </c>
       <c r="P53">
-        <v>-1.5918327824</v>
+        <v>-1.6415224448</v>
       </c>
       <c r="Q53">
-        <v>-0.5618327824000005</v>
+        <v>-0.6115224448000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1026653810454673</v>
+        <v>0.1038500764839146</v>
       </c>
       <c r="T53">
-        <v>1.313288245853749</v>
+        <v>1.340648417642369</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09593809928372307</v>
+        <v>0.09409313583595919</v>
       </c>
       <c r="W53">
-        <v>0.2131777961888981</v>
+        <v>0.2136128385698808</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3718530979989266</v>
+        <v>0.3647020768835626</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.160926712768617</v>
+        <v>0.162826712768617</v>
       </c>
       <c r="C54">
-        <v>-8.796294662944524</v>
+        <v>-9.169715615587155</v>
       </c>
       <c r="D54">
-        <v>5.507705337055475</v>
+        <v>5.418284384412844</v>
       </c>
       <c r="E54">
-        <v>-3.132</v>
+        <v>-2.847999999999999</v>
       </c>
       <c r="F54">
-        <v>14.768</v>
+        <v>15.052</v>
       </c>
       <c r="G54">
         <v>0.464</v>
@@ -5715,37 +5715,37 @@
         <v>1.27</v>
       </c>
       <c r="M54">
-        <v>3.4822944</v>
+        <v>3.5492616</v>
       </c>
       <c r="N54">
-        <v>-2.2122944</v>
+        <v>-2.2792616</v>
       </c>
       <c r="O54">
-        <v>-0.5707719552000001</v>
+        <v>-0.5880494928</v>
       </c>
       <c r="P54">
-        <v>-1.6415224448</v>
+        <v>-1.6912121072</v>
       </c>
       <c r="Q54">
-        <v>-0.6115224448000001</v>
+        <v>-0.6612121071999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1038500764839146</v>
+        <v>0.1050851844942106</v>
       </c>
       <c r="T54">
-        <v>1.340648417642369</v>
+        <v>1.369172852060292</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09409313583595919</v>
+        <v>0.09231779365037504</v>
       </c>
       <c r="W54">
-        <v>0.2136128385698808</v>
+        <v>0.2140314642572416</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3647020768835626</v>
+        <v>0.3578209056216087</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.162826712768617</v>
+        <v>0.164726712768617</v>
       </c>
       <c r="C55">
-        <v>-9.169715615587155</v>
+        <v>-9.540279349593778</v>
       </c>
       <c r="D55">
-        <v>5.418284384412844</v>
+        <v>5.331720650406221</v>
       </c>
       <c r="E55">
-        <v>-2.847999999999999</v>
+        <v>-2.563999999999998</v>
       </c>
       <c r="F55">
-        <v>15.052</v>
+        <v>15.336</v>
       </c>
       <c r="G55">
         <v>0.464</v>
@@ -5797,37 +5797,37 @@
         <v>1.27</v>
       </c>
       <c r="M55">
-        <v>3.5492616</v>
+        <v>3.6162288</v>
       </c>
       <c r="N55">
-        <v>-2.2792616</v>
+        <v>-2.3462288</v>
       </c>
       <c r="O55">
-        <v>-0.5880494928</v>
+        <v>-0.6053270304000001</v>
       </c>
       <c r="P55">
-        <v>-1.6912121072</v>
+        <v>-1.7409017696</v>
       </c>
       <c r="Q55">
-        <v>-0.6612121071999999</v>
+        <v>-0.7109017696000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1050851844942106</v>
+        <v>0.1063739928527804</v>
       </c>
       <c r="T55">
-        <v>1.369172852060292</v>
+        <v>1.398937479278994</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09231779365037504</v>
+        <v>0.0906082048790718</v>
       </c>
       <c r="W55">
-        <v>0.2140314642572416</v>
+        <v>0.2144345852895149</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3578209056216087</v>
+        <v>0.3511945925545418</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.164726712768617</v>
+        <v>0.166626712768617</v>
       </c>
       <c r="C56">
-        <v>-9.540279349593778</v>
+        <v>-9.90812065424941</v>
       </c>
       <c r="D56">
-        <v>5.331720650406221</v>
+        <v>5.24787934575059</v>
       </c>
       <c r="E56">
-        <v>-2.563999999999998</v>
+        <v>-2.279999999999998</v>
       </c>
       <c r="F56">
-        <v>15.336</v>
+        <v>15.62</v>
       </c>
       <c r="G56">
         <v>0.464</v>
@@ -5879,37 +5879,37 @@
         <v>1.27</v>
       </c>
       <c r="M56">
-        <v>3.6162288</v>
+        <v>3.683196000000001</v>
       </c>
       <c r="N56">
-        <v>-2.3462288</v>
+        <v>-2.413196000000001</v>
       </c>
       <c r="O56">
-        <v>-0.6053270304000001</v>
+        <v>-0.6226045680000003</v>
       </c>
       <c r="P56">
-        <v>-1.7409017696</v>
+        <v>-1.790591432000001</v>
       </c>
       <c r="Q56">
-        <v>-0.7109017696000002</v>
+        <v>-0.7605914320000007</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1063739928527804</v>
+        <v>0.1077200815828422</v>
       </c>
       <c r="T56">
-        <v>1.398937479278994</v>
+        <v>1.430024978818527</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0906082048790718</v>
+        <v>0.08896078297217958</v>
       </c>
       <c r="W56">
-        <v>0.2144345852895149</v>
+        <v>0.2148230473751601</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3511945925545418</v>
+        <v>0.3448092363262774</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.166626712768617</v>
+        <v>0.168526712768617</v>
       </c>
       <c r="C57">
-        <v>-9.90812065424941</v>
+        <v>-10.2733659718497</v>
       </c>
       <c r="D57">
-        <v>5.24787934575059</v>
+        <v>5.166634028150299</v>
       </c>
       <c r="E57">
-        <v>-2.279999999999998</v>
+        <v>-1.995999999999999</v>
       </c>
       <c r="F57">
-        <v>15.62</v>
+        <v>15.904</v>
       </c>
       <c r="G57">
         <v>0.464</v>
@@ -5961,37 +5961,37 @@
         <v>1.27</v>
       </c>
       <c r="M57">
-        <v>3.683196000000001</v>
+        <v>3.7501632</v>
       </c>
       <c r="N57">
-        <v>-2.413196000000001</v>
+        <v>-2.480163200000001</v>
       </c>
       <c r="O57">
-        <v>-0.6226045680000003</v>
+        <v>-0.6398821056000001</v>
       </c>
       <c r="P57">
-        <v>-1.790591432000001</v>
+        <v>-1.840281094400001</v>
       </c>
       <c r="Q57">
-        <v>-0.7605914320000007</v>
+        <v>-0.8102810944000005</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1077200815828422</v>
+        <v>0.1091273561642704</v>
       </c>
       <c r="T57">
-        <v>1.430024978818527</v>
+        <v>1.462525546518948</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08896078297217958</v>
+        <v>0.08737219756196209</v>
       </c>
       <c r="W57">
-        <v>0.2148230473751601</v>
+        <v>0.2151976358148893</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3448092363262774</v>
+        <v>0.3386519285347367</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.168526712768617</v>
+        <v>0.170426712768617</v>
       </c>
       <c r="C58">
-        <v>-10.2733659718497</v>
+        <v>-10.63613403397224</v>
       </c>
       <c r="D58">
-        <v>5.166634028150299</v>
+        <v>5.087865966027764</v>
       </c>
       <c r="E58">
-        <v>-1.995999999999999</v>
+        <v>-1.711999999999996</v>
       </c>
       <c r="F58">
-        <v>15.904</v>
+        <v>16.188</v>
       </c>
       <c r="G58">
         <v>0.464</v>
@@ -6043,37 +6043,37 @@
         <v>1.27</v>
       </c>
       <c r="M58">
-        <v>3.7501632</v>
+        <v>3.817130400000001</v>
       </c>
       <c r="N58">
-        <v>-2.480163200000001</v>
+        <v>-2.547130400000001</v>
       </c>
       <c r="O58">
-        <v>-0.6398821056000001</v>
+        <v>-0.6571596432000003</v>
       </c>
       <c r="P58">
-        <v>-1.840281094400001</v>
+        <v>-1.889970756800001</v>
       </c>
       <c r="Q58">
-        <v>-0.8102810944000005</v>
+        <v>-0.8599707568000008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1091273561642704</v>
+        <v>0.110600085377393</v>
       </c>
       <c r="T58">
-        <v>1.462525546518948</v>
+        <v>1.496537768531017</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08737219756196209</v>
+        <v>0.08583935199069959</v>
       </c>
       <c r="W58">
-        <v>0.2151976358148893</v>
+        <v>0.2155590808005931</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3386519285347367</v>
+        <v>0.3327106666306184</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.170426712768617</v>
+        <v>0.1723267127686171</v>
       </c>
       <c r="C59">
-        <v>-10.63613403397224</v>
+        <v>-10.99653644042004</v>
       </c>
       <c r="D59">
-        <v>5.087865966027764</v>
+        <v>5.011463559579957</v>
       </c>
       <c r="E59">
-        <v>-1.711999999999996</v>
+        <v>-1.427999999999997</v>
       </c>
       <c r="F59">
-        <v>16.188</v>
+        <v>16.472</v>
       </c>
       <c r="G59">
         <v>0.464</v>
@@ -6125,37 +6125,37 @@
         <v>1.27</v>
       </c>
       <c r="M59">
-        <v>3.817130400000001</v>
+        <v>3.8840976</v>
       </c>
       <c r="N59">
-        <v>-2.547130400000001</v>
+        <v>-2.614097600000001</v>
       </c>
       <c r="O59">
-        <v>-0.6571596432000003</v>
+        <v>-0.6744371808000003</v>
       </c>
       <c r="P59">
-        <v>-1.889970756800001</v>
+        <v>-1.939660419200001</v>
       </c>
       <c r="Q59">
-        <v>-0.8599707568000008</v>
+        <v>-0.9096604192000006</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.110600085377393</v>
+        <v>0.1121429445530452</v>
       </c>
       <c r="T59">
-        <v>1.496537768531017</v>
+        <v>1.532169620162708</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08583935199069959</v>
+        <v>0.08435936316327373</v>
       </c>
       <c r="W59">
-        <v>0.2155590808005931</v>
+        <v>0.2159080621661001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3327106666306184</v>
+        <v>0.3269742758266423</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.172326712768617</v>
+        <v>0.174226712768617</v>
       </c>
       <c r="C60">
-        <v>-10.99653644042004</v>
+        <v>-11.35467818677429</v>
       </c>
       <c r="D60">
-        <v>5.011463559579961</v>
+        <v>4.937321813225704</v>
       </c>
       <c r="E60">
-        <v>-1.428000000000001</v>
+        <v>-1.144000000000002</v>
       </c>
       <c r="F60">
-        <v>16.472</v>
+        <v>16.756</v>
       </c>
       <c r="G60">
         <v>0.464</v>
@@ -6207,37 +6207,37 @@
         <v>1.27</v>
       </c>
       <c r="M60">
-        <v>3.8840976</v>
+        <v>3.951064799999999</v>
       </c>
       <c r="N60">
-        <v>-2.6140976</v>
+        <v>-2.6810648</v>
       </c>
       <c r="O60">
-        <v>-0.6744371808</v>
+        <v>-0.6917147184</v>
       </c>
       <c r="P60">
-        <v>-1.9396604192</v>
+        <v>-1.9893500816</v>
       </c>
       <c r="Q60">
-        <v>-0.9096604192</v>
+        <v>-0.9593500815999996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1121429445530452</v>
+        <v>0.1137610651519</v>
       </c>
       <c r="T60">
-        <v>1.532169620162707</v>
+        <v>1.569539610898383</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08435936316327376</v>
+        <v>0.08292954344864201</v>
       </c>
       <c r="W60">
-        <v>0.2159080621661001</v>
+        <v>0.2162452136548102</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3269742758266424</v>
+        <v>0.3214323389482248</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.174226712768617</v>
+        <v>0.176126712768617</v>
       </c>
       <c r="C61">
-        <v>-11.35467818677429</v>
+        <v>-11.71065814580068</v>
       </c>
       <c r="D61">
-        <v>4.937321813225704</v>
+        <v>4.865341854199315</v>
       </c>
       <c r="E61">
-        <v>-1.144000000000002</v>
+        <v>-0.8599999999999994</v>
       </c>
       <c r="F61">
-        <v>16.756</v>
+        <v>17.04</v>
       </c>
       <c r="G61">
         <v>0.464</v>
@@ -6289,37 +6289,37 @@
         <v>1.27</v>
       </c>
       <c r="M61">
-        <v>3.951064799999999</v>
+        <v>4.018032</v>
       </c>
       <c r="N61">
-        <v>-2.6810648</v>
+        <v>-2.748032</v>
       </c>
       <c r="O61">
-        <v>-0.6917147184</v>
+        <v>-0.708992256</v>
       </c>
       <c r="P61">
-        <v>-1.9893500816</v>
+        <v>-2.039039744</v>
       </c>
       <c r="Q61">
-        <v>-0.9593500815999996</v>
+        <v>-1.009039744</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1137610651519</v>
+        <v>0.1154600917806975</v>
       </c>
       <c r="T61">
-        <v>1.569539610898383</v>
+        <v>1.608778101170843</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08292954344864201</v>
+        <v>0.08154738439116462</v>
       </c>
       <c r="W61">
-        <v>0.2162452136548102</v>
+        <v>0.2165711267605634</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3214323389482248</v>
+        <v>0.3160751332990877</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.176126712768617</v>
+        <v>0.178026712768617</v>
       </c>
       <c r="C62">
-        <v>-11.71065814580068</v>
+        <v>-12.06456950735102</v>
       </c>
       <c r="D62">
-        <v>4.865341854199315</v>
+        <v>4.795430492648983</v>
       </c>
       <c r="E62">
-        <v>-0.8599999999999994</v>
+        <v>-0.5760000000000005</v>
       </c>
       <c r="F62">
-        <v>17.04</v>
+        <v>17.324</v>
       </c>
       <c r="G62">
         <v>0.464</v>
@@ -6371,37 +6371,37 @@
         <v>1.27</v>
       </c>
       <c r="M62">
-        <v>4.018032</v>
+        <v>4.084999199999999</v>
       </c>
       <c r="N62">
-        <v>-2.748032</v>
+        <v>-2.8149992</v>
       </c>
       <c r="O62">
-        <v>-0.708992256</v>
+        <v>-0.7262697936</v>
       </c>
       <c r="P62">
-        <v>-2.039039744</v>
+        <v>-2.0887294064</v>
       </c>
       <c r="Q62">
-        <v>-1.009039744</v>
+        <v>-1.0587294064</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1154600917806975</v>
+        <v>0.1172462479802026</v>
       </c>
       <c r="T62">
-        <v>1.608778101170843</v>
+        <v>1.650028821713685</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08154738439116462</v>
+        <v>0.08021054202409636</v>
       </c>
       <c r="W62">
-        <v>0.2165711267605634</v>
+        <v>0.2168863541907181</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3160751332990877</v>
+        <v>0.3108935737368075</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.178026712768617</v>
+        <v>0.179926712768617</v>
       </c>
       <c r="C63">
-        <v>-12.06456950735102</v>
+        <v>-12.41650018087577</v>
       </c>
       <c r="D63">
-        <v>4.795430492648983</v>
+        <v>4.72749981912423</v>
       </c>
       <c r="E63">
-        <v>-0.5760000000000005</v>
+        <v>-0.291999999999998</v>
       </c>
       <c r="F63">
-        <v>17.324</v>
+        <v>17.608</v>
       </c>
       <c r="G63">
         <v>0.464</v>
@@ -6453,37 +6453,37 @@
         <v>1.27</v>
       </c>
       <c r="M63">
-        <v>4.084999199999999</v>
+        <v>4.1519664</v>
       </c>
       <c r="N63">
-        <v>-2.8149992</v>
+        <v>-2.8819664</v>
       </c>
       <c r="O63">
-        <v>-0.7262697936</v>
+        <v>-0.7435473312000002</v>
       </c>
       <c r="P63">
-        <v>-2.0887294064</v>
+        <v>-2.1384190688</v>
       </c>
       <c r="Q63">
-        <v>-1.0587294064</v>
+        <v>-1.1084190688</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1172462479802026</v>
+        <v>0.1191264124007342</v>
       </c>
       <c r="T63">
-        <v>1.650028821713685</v>
+        <v>1.693450632811414</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08021054202409636</v>
+        <v>0.07891682360435286</v>
       </c>
       <c r="W63">
-        <v>0.2168863541907181</v>
+        <v>0.2171914129940936</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3108935737368075</v>
+        <v>0.3058791612571815</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.179926712768617</v>
+        <v>0.181826712768617</v>
       </c>
       <c r="C64">
-        <v>-12.41650018087577</v>
+        <v>-12.7665331642032</v>
       </c>
       <c r="D64">
-        <v>4.72749981912423</v>
+        <v>4.661466835796797</v>
       </c>
       <c r="E64">
-        <v>-0.291999999999998</v>
+        <v>-0.007999999999999119</v>
       </c>
       <c r="F64">
-        <v>17.608</v>
+        <v>17.892</v>
       </c>
       <c r="G64">
         <v>0.464</v>
@@ -6535,37 +6535,37 @@
         <v>1.27</v>
       </c>
       <c r="M64">
-        <v>4.1519664</v>
+        <v>4.2189336</v>
       </c>
       <c r="N64">
-        <v>-2.8819664</v>
+        <v>-2.9489336</v>
       </c>
       <c r="O64">
-        <v>-0.7435473312000002</v>
+        <v>-0.7608248688000001</v>
       </c>
       <c r="P64">
-        <v>-2.1384190688</v>
+        <v>-2.1881087312</v>
       </c>
       <c r="Q64">
-        <v>-1.1084190688</v>
+        <v>-1.1581087312</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1191264124007342</v>
+        <v>0.1211082073304837</v>
       </c>
       <c r="T64">
-        <v>1.693450632811414</v>
+        <v>1.739219568833343</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07891682360435286</v>
+        <v>0.07766417561063298</v>
       </c>
       <c r="W64">
-        <v>0.2171914129940936</v>
+        <v>0.2174867873910127</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3058791612571815</v>
+        <v>0.3010239364753216</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.181826712768617</v>
+        <v>0.183726712768617</v>
       </c>
       <c r="C65">
-        <v>-12.7665331642032</v>
+        <v>-13.11474688183796</v>
       </c>
       <c r="D65">
-        <v>4.661466835796797</v>
+        <v>4.597253118162038</v>
       </c>
       <c r="E65">
-        <v>-0.007999999999999119</v>
+        <v>0.2759999999999998</v>
       </c>
       <c r="F65">
-        <v>17.892</v>
+        <v>18.176</v>
       </c>
       <c r="G65">
         <v>0.464</v>
@@ -6617,37 +6617,37 @@
         <v>1.27</v>
       </c>
       <c r="M65">
-        <v>4.2189336</v>
+        <v>4.285900799999999</v>
       </c>
       <c r="N65">
-        <v>-2.9489336</v>
+        <v>-3.0159008</v>
       </c>
       <c r="O65">
-        <v>-0.7608248688000001</v>
+        <v>-0.7781024063999999</v>
       </c>
       <c r="P65">
-        <v>-2.1881087312</v>
+        <v>-2.2377983936</v>
       </c>
       <c r="Q65">
-        <v>-1.1581087312</v>
+        <v>-1.2077983936</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1211082073304837</v>
+        <v>0.1232001019785528</v>
       </c>
       <c r="T65">
-        <v>1.739219568833343</v>
+        <v>1.787531223523159</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07766417561063298</v>
+        <v>0.07645067286671683</v>
       </c>
       <c r="W65">
-        <v>0.2174867873910127</v>
+        <v>0.2177729313380282</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3010239364753216</v>
+        <v>0.2963204374678947</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.183726712768617</v>
+        <v>0.185626712768617</v>
       </c>
       <c r="C66">
-        <v>-13.11474688183796</v>
+        <v>-13.46121549567831</v>
       </c>
       <c r="D66">
-        <v>4.597253118162038</v>
+        <v>4.534784504321693</v>
       </c>
       <c r="E66">
-        <v>0.2759999999999998</v>
+        <v>0.5600000000000023</v>
       </c>
       <c r="F66">
-        <v>18.176</v>
+        <v>18.46</v>
       </c>
       <c r="G66">
         <v>0.464</v>
@@ -6699,37 +6699,37 @@
         <v>1.27</v>
       </c>
       <c r="M66">
-        <v>4.285900799999999</v>
+        <v>4.352868</v>
       </c>
       <c r="N66">
-        <v>-3.0159008</v>
+        <v>-3.082868</v>
       </c>
       <c r="O66">
-        <v>-0.7781024063999999</v>
+        <v>-0.7953799440000001</v>
       </c>
       <c r="P66">
-        <v>-2.2377983936</v>
+        <v>-2.287488056</v>
       </c>
       <c r="Q66">
-        <v>-1.2077983936</v>
+        <v>-1.257488056</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1232001019785528</v>
+        <v>0.1254115334636543</v>
       </c>
       <c r="T66">
-        <v>1.787531223523159</v>
+        <v>1.838603544195249</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07645067286671683</v>
+        <v>0.07527450866876735</v>
       </c>
       <c r="W66">
-        <v>0.2177729313380282</v>
+        <v>0.2180502708559047</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2963204374678947</v>
+        <v>0.2917616615068501</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.185626712768617</v>
+        <v>0.187526712768617</v>
       </c>
       <c r="C67">
-        <v>-13.46121549567831</v>
+        <v>-13.80600919074042</v>
       </c>
       <c r="D67">
-        <v>4.534784504321693</v>
+        <v>4.473990809259576</v>
       </c>
       <c r="E67">
-        <v>0.5600000000000023</v>
+        <v>0.8440000000000012</v>
       </c>
       <c r="F67">
-        <v>18.46</v>
+        <v>18.744</v>
       </c>
       <c r="G67">
         <v>0.464</v>
@@ -6781,37 +6781,37 @@
         <v>1.27</v>
       </c>
       <c r="M67">
-        <v>4.352868</v>
+        <v>4.419835200000001</v>
       </c>
       <c r="N67">
-        <v>-3.082868</v>
+        <v>-3.149835200000001</v>
       </c>
       <c r="O67">
-        <v>-0.7953799440000001</v>
+        <v>-0.8126574816000003</v>
       </c>
       <c r="P67">
-        <v>-2.287488056</v>
+        <v>-2.3371777184</v>
       </c>
       <c r="Q67">
-        <v>-1.257488056</v>
+        <v>-1.3071777184</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1254115334636543</v>
+        <v>0.1277530491537618</v>
       </c>
       <c r="T67">
-        <v>1.838603544195249</v>
+        <v>1.892680119024521</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07527450866876735</v>
+        <v>0.07413398581014964</v>
       </c>
       <c r="W67">
-        <v>0.2180502708559047</v>
+        <v>0.2183192061459667</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2917616615068501</v>
+        <v>0.2873410302718978</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.187526712768617</v>
+        <v>0.189426712768617</v>
       </c>
       <c r="C68">
-        <v>-13.80600919074042</v>
+        <v>-14.14919443820402</v>
       </c>
       <c r="D68">
-        <v>4.473990809259576</v>
+        <v>4.414805561795982</v>
       </c>
       <c r="E68">
-        <v>0.8440000000000012</v>
+        <v>1.128</v>
       </c>
       <c r="F68">
-        <v>18.744</v>
+        <v>19.028</v>
       </c>
       <c r="G68">
         <v>0.464</v>
@@ -6863,37 +6863,37 @@
         <v>1.27</v>
       </c>
       <c r="M68">
-        <v>4.419835200000001</v>
+        <v>4.4868024</v>
       </c>
       <c r="N68">
-        <v>-3.149835200000001</v>
+        <v>-3.216802400000001</v>
       </c>
       <c r="O68">
-        <v>-0.8126574816000003</v>
+        <v>-0.8299350192000002</v>
       </c>
       <c r="P68">
-        <v>-2.3371777184</v>
+        <v>-2.3868673808</v>
       </c>
       <c r="Q68">
-        <v>-1.3071777184</v>
+        <v>-1.3568673808</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1277530491537618</v>
+        <v>0.1302364748856939</v>
       </c>
       <c r="T68">
-        <v>1.892680119024521</v>
+        <v>1.950034062025265</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07413398581014964</v>
+        <v>0.07302750840999817</v>
       </c>
       <c r="W68">
-        <v>0.2183192061459667</v>
+        <v>0.2185801135169224</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2873410302718978</v>
+        <v>0.2830523581782874</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.189426712768617</v>
+        <v>0.1913267127686171</v>
       </c>
       <c r="C69">
-        <v>-14.14919443820402</v>
+        <v>-14.490834237852</v>
       </c>
       <c r="D69">
-        <v>4.414805561795982</v>
+        <v>4.357165762148</v>
       </c>
       <c r="E69">
-        <v>1.128</v>
+        <v>1.412000000000003</v>
       </c>
       <c r="F69">
-        <v>19.028</v>
+        <v>19.312</v>
       </c>
       <c r="G69">
         <v>0.464</v>
@@ -6945,37 +6945,37 @@
         <v>1.27</v>
       </c>
       <c r="M69">
-        <v>4.4868024</v>
+        <v>4.553769600000001</v>
       </c>
       <c r="N69">
-        <v>-3.216802400000001</v>
+        <v>-3.283769600000001</v>
       </c>
       <c r="O69">
-        <v>-0.8299350192000002</v>
+        <v>-0.8472125568000003</v>
       </c>
       <c r="P69">
-        <v>-2.3868673808</v>
+        <v>-2.436557043200001</v>
       </c>
       <c r="Q69">
-        <v>-1.3568673808</v>
+        <v>-1.406557043200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1302364748856939</v>
+        <v>0.1328751147258719</v>
       </c>
       <c r="T69">
-        <v>1.950034062025265</v>
+        <v>2.010972626463554</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07302750840999817</v>
+        <v>0.0719535744627923</v>
       </c>
       <c r="W69">
-        <v>0.2185801135169224</v>
+        <v>0.2188333471416736</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2830523581782874</v>
+        <v>0.2788898234991949</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1913267127686171</v>
+        <v>0.193226712768617</v>
       </c>
       <c r="C70">
-        <v>-14.490834237852</v>
+        <v>-14.8309883417631</v>
       </c>
       <c r="D70">
-        <v>4.357165762148</v>
+        <v>4.3010116582369</v>
       </c>
       <c r="E70">
-        <v>1.412000000000003</v>
+        <v>1.696000000000002</v>
       </c>
       <c r="F70">
-        <v>19.312</v>
+        <v>19.596</v>
       </c>
       <c r="G70">
         <v>0.464</v>
@@ -7027,37 +7027,37 @@
         <v>1.27</v>
       </c>
       <c r="M70">
-        <v>4.553769600000001</v>
+        <v>4.6207368</v>
       </c>
       <c r="N70">
-        <v>-3.283769600000001</v>
+        <v>-3.350736800000001</v>
       </c>
       <c r="O70">
-        <v>-0.8472125568000003</v>
+        <v>-0.8644900944000002</v>
       </c>
       <c r="P70">
-        <v>-2.436557043200001</v>
+        <v>-2.486246705600001</v>
       </c>
       <c r="Q70">
-        <v>-1.406557043200001</v>
+        <v>-1.456246705600001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1328751147258719</v>
+        <v>0.1356839893944484</v>
       </c>
       <c r="T70">
-        <v>2.010972626463554</v>
+        <v>2.075842711188185</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0719535744627923</v>
+        <v>0.07091076903579532</v>
       </c>
       <c r="W70">
-        <v>0.2188333471416736</v>
+        <v>0.2190792406613595</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2788898234991949</v>
+        <v>0.2748479419992066</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.193226712768617</v>
+        <v>0.195126712768617</v>
       </c>
       <c r="C71">
-        <v>-14.8309883417631</v>
+        <v>-15.16971346092723</v>
       </c>
       <c r="D71">
-        <v>4.3010116582369</v>
+        <v>4.24628653907277</v>
       </c>
       <c r="E71">
-        <v>1.696000000000002</v>
+        <v>1.980000000000004</v>
       </c>
       <c r="F71">
-        <v>19.596</v>
+        <v>19.88</v>
       </c>
       <c r="G71">
         <v>0.464</v>
@@ -7109,37 +7109,37 @@
         <v>1.27</v>
       </c>
       <c r="M71">
-        <v>4.6207368</v>
+        <v>4.687704000000001</v>
       </c>
       <c r="N71">
-        <v>-3.350736800000001</v>
+        <v>-3.417704000000001</v>
       </c>
       <c r="O71">
-        <v>-0.8644900944000002</v>
+        <v>-0.8817676320000004</v>
       </c>
       <c r="P71">
-        <v>-2.486246705600001</v>
+        <v>-2.535936368000001</v>
       </c>
       <c r="Q71">
-        <v>-1.456246705600001</v>
+        <v>-1.505936368000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1356839893944484</v>
+        <v>0.1386801223742633</v>
       </c>
       <c r="T71">
-        <v>2.075842711188185</v>
+        <v>2.145037468227791</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07091076903579532</v>
+        <v>0.06989775804956966</v>
       </c>
       <c r="W71">
-        <v>0.2190792406613595</v>
+        <v>0.2193181086519115</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2748479419992066</v>
+        <v>0.2709215428277894</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.195126712768617</v>
+        <v>0.197026712768617</v>
       </c>
       <c r="C72">
-        <v>-15.16971346092723</v>
+        <v>-15.50706345628541</v>
       </c>
       <c r="D72">
-        <v>4.24628653907277</v>
+        <v>4.192936543714594</v>
       </c>
       <c r="E72">
-        <v>1.980000000000004</v>
+        <v>2.264000000000003</v>
       </c>
       <c r="F72">
-        <v>19.88</v>
+        <v>20.164</v>
       </c>
       <c r="G72">
         <v>0.464</v>
@@ -7191,37 +7191,37 @@
         <v>1.27</v>
       </c>
       <c r="M72">
-        <v>4.687704000000001</v>
+        <v>4.754671200000001</v>
       </c>
       <c r="N72">
-        <v>-3.417704000000001</v>
+        <v>-3.484671200000001</v>
       </c>
       <c r="O72">
-        <v>-0.8817676320000004</v>
+        <v>-0.8990451696000002</v>
       </c>
       <c r="P72">
-        <v>-2.535936368000001</v>
+        <v>-2.585626030400001</v>
       </c>
       <c r="Q72">
-        <v>-1.505936368000001</v>
+        <v>-1.555626030400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1386801223742633</v>
+        <v>0.1418828852147552</v>
       </c>
       <c r="T72">
-        <v>2.145037468227791</v>
+        <v>2.219004277477025</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06989775804956966</v>
+        <v>0.06891328258408276</v>
       </c>
       <c r="W72">
-        <v>0.2193181086519115</v>
+        <v>0.2195502479666733</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2709215428277894</v>
+        <v>0.2671057464499331</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.197026712768617</v>
+        <v>0.198926712768617</v>
       </c>
       <c r="C73">
-        <v>-15.5070634562854</v>
+        <v>-15.84308951554716</v>
       </c>
       <c r="D73">
-        <v>4.192936543714594</v>
+        <v>4.14091048445284</v>
       </c>
       <c r="E73">
-        <v>2.263999999999999</v>
+        <v>2.547999999999998</v>
       </c>
       <c r="F73">
-        <v>20.164</v>
+        <v>20.448</v>
       </c>
       <c r="G73">
         <v>0.464</v>
@@ -7273,37 +7273,37 @@
         <v>1.27</v>
       </c>
       <c r="M73">
-        <v>4.7546712</v>
+        <v>4.821638399999999</v>
       </c>
       <c r="N73">
-        <v>-3.4846712</v>
+        <v>-3.5516384</v>
       </c>
       <c r="O73">
-        <v>-0.8990451696</v>
+        <v>-0.9163227072</v>
       </c>
       <c r="P73">
-        <v>-2.5856260304</v>
+        <v>-2.6353156928</v>
       </c>
       <c r="Q73">
-        <v>-1.5556260304</v>
+        <v>-1.6053156928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1418828852147551</v>
+        <v>0.1453144168295678</v>
       </c>
       <c r="T73">
-        <v>2.219004277477024</v>
+        <v>2.298254430244061</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06891328258408277</v>
+        <v>0.06795615365930385</v>
       </c>
       <c r="W73">
-        <v>0.2195502479666733</v>
+        <v>0.2197759389671362</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2671057464499332</v>
+        <v>0.2633959444159064</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.198926712768617</v>
+        <v>0.200826712768617</v>
       </c>
       <c r="C74">
-        <v>-15.84308951554716</v>
+        <v>-16.17784031700551</v>
       </c>
       <c r="D74">
-        <v>4.14091048445284</v>
+        <v>4.090159682994492</v>
       </c>
       <c r="E74">
-        <v>2.547999999999998</v>
+        <v>2.832000000000001</v>
       </c>
       <c r="F74">
-        <v>20.448</v>
+        <v>20.732</v>
       </c>
       <c r="G74">
         <v>0.464</v>
@@ -7355,37 +7355,37 @@
         <v>1.27</v>
       </c>
       <c r="M74">
-        <v>4.821638399999999</v>
+        <v>4.8886056</v>
       </c>
       <c r="N74">
-        <v>-3.5516384</v>
+        <v>-3.6186056</v>
       </c>
       <c r="O74">
-        <v>-0.9163227072</v>
+        <v>-0.9336002448000001</v>
       </c>
       <c r="P74">
-        <v>-2.6353156928</v>
+        <v>-2.6850053552</v>
       </c>
       <c r="Q74">
-        <v>-1.6053156928</v>
+        <v>-1.6550053552</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1453144168295678</v>
+        <v>0.1490001359714037</v>
       </c>
       <c r="T74">
-        <v>2.298254430244061</v>
+        <v>2.383374964697544</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06795615365930385</v>
+        <v>0.06702524744479284</v>
       </c>
       <c r="W74">
-        <v>0.2197759389671362</v>
+        <v>0.2199954466525179</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2633959444159064</v>
+        <v>0.2597877807937706</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.200826712768617</v>
+        <v>0.202726712768617</v>
       </c>
       <c r="C75">
-        <v>-16.17784031700551</v>
+        <v>-16.51136218145154</v>
       </c>
       <c r="D75">
-        <v>4.090159682994492</v>
+        <v>4.040637818548455</v>
       </c>
       <c r="E75">
-        <v>2.832000000000001</v>
+        <v>3.116</v>
       </c>
       <c r="F75">
-        <v>20.732</v>
+        <v>21.016</v>
       </c>
       <c r="G75">
         <v>0.464</v>
@@ -7437,37 +7437,37 @@
         <v>1.27</v>
       </c>
       <c r="M75">
-        <v>4.8886056</v>
+        <v>4.9555728</v>
       </c>
       <c r="N75">
-        <v>-3.6186056</v>
+        <v>-3.6855728</v>
       </c>
       <c r="O75">
-        <v>-0.9336002448000001</v>
+        <v>-0.9508777824000001</v>
       </c>
       <c r="P75">
-        <v>-2.6850053552</v>
+        <v>-2.7346950176</v>
       </c>
       <c r="Q75">
-        <v>-1.6550053552</v>
+        <v>-1.7046950176</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1490001359714037</v>
+        <v>0.1529693719703038</v>
       </c>
       <c r="T75">
-        <v>2.383374964697544</v>
+        <v>2.475043232570527</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06702524744479284</v>
+        <v>0.06611950085770105</v>
       </c>
       <c r="W75">
-        <v>0.2199954466525179</v>
+        <v>0.2202090216977541</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2597877807937706</v>
+        <v>0.2562771351073684</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.202726712768617</v>
+        <v>0.204626712768617</v>
       </c>
       <c r="C76">
-        <v>-16.51136218145154</v>
+        <v>-16.84369921318516</v>
       </c>
       <c r="D76">
-        <v>4.040637818548455</v>
+        <v>3.992300786814841</v>
       </c>
       <c r="E76">
-        <v>3.116</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="F76">
-        <v>21.016</v>
+        <v>21.3</v>
       </c>
       <c r="G76">
         <v>0.464</v>
@@ -7519,37 +7519,37 @@
         <v>1.27</v>
       </c>
       <c r="M76">
-        <v>4.9555728</v>
+        <v>5.022539999999999</v>
       </c>
       <c r="N76">
-        <v>-3.6855728</v>
+        <v>-3.75254</v>
       </c>
       <c r="O76">
-        <v>-0.9508777824000001</v>
+        <v>-0.9681553199999999</v>
       </c>
       <c r="P76">
-        <v>-2.7346950176</v>
+        <v>-2.78438468</v>
       </c>
       <c r="Q76">
-        <v>-1.7046950176</v>
+        <v>-1.75438468</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1529693719703038</v>
+        <v>0.157256146849116</v>
       </c>
       <c r="T76">
-        <v>2.475043232570527</v>
+        <v>2.574044961873349</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06611950085770105</v>
+        <v>0.06523790751293171</v>
       </c>
       <c r="W76">
-        <v>0.2202090216977541</v>
+        <v>0.2204169014084507</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2562771351073684</v>
+        <v>0.2528601066392702</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.204626712768617</v>
+        <v>0.206526712768617</v>
       </c>
       <c r="C77">
-        <v>-16.84369921318516</v>
+        <v>-17.17489343102416</v>
       </c>
       <c r="D77">
-        <v>3.992300786814841</v>
+        <v>3.945106568975844</v>
       </c>
       <c r="E77">
-        <v>3.399999999999999</v>
+        <v>3.684000000000001</v>
       </c>
       <c r="F77">
-        <v>21.3</v>
+        <v>21.584</v>
       </c>
       <c r="G77">
         <v>0.464</v>
@@ -7601,37 +7601,37 @@
         <v>1.27</v>
       </c>
       <c r="M77">
-        <v>5.022539999999999</v>
+        <v>5.0895072</v>
       </c>
       <c r="N77">
-        <v>-3.75254</v>
+        <v>-3.8195072</v>
       </c>
       <c r="O77">
-        <v>-0.9681553199999999</v>
+        <v>-0.9854328576000001</v>
       </c>
       <c r="P77">
-        <v>-2.78438468</v>
+        <v>-2.8340743424</v>
       </c>
       <c r="Q77">
-        <v>-1.75438468</v>
+        <v>-1.8040743424</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.157256146849116</v>
+        <v>0.1619001529678291</v>
       </c>
       <c r="T77">
-        <v>2.574044961873349</v>
+        <v>2.681296835284738</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06523790751293171</v>
+        <v>0.0643795139930247</v>
       </c>
       <c r="W77">
-        <v>0.2204169014084507</v>
+        <v>0.2206193106004448</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2528601066392702</v>
+        <v>0.2495329999729639</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.206526712768617</v>
+        <v>0.208426712768617</v>
       </c>
       <c r="C78">
-        <v>-17.17489343102416</v>
+        <v>-17.50498489012976</v>
       </c>
       <c r="D78">
-        <v>3.945106568975844</v>
+        <v>3.899015109870234</v>
       </c>
       <c r="E78">
-        <v>3.684000000000001</v>
+        <v>3.968</v>
       </c>
       <c r="F78">
-        <v>21.584</v>
+        <v>21.868</v>
       </c>
       <c r="G78">
         <v>0.464</v>
@@ -7683,37 +7683,37 @@
         <v>1.27</v>
       </c>
       <c r="M78">
-        <v>5.0895072</v>
+        <v>5.1564744</v>
       </c>
       <c r="N78">
-        <v>-3.8195072</v>
+        <v>-3.8864744</v>
       </c>
       <c r="O78">
-        <v>-0.9854328576000001</v>
+        <v>-1.0027103952</v>
       </c>
       <c r="P78">
-        <v>-2.8340743424</v>
+        <v>-2.8837640048</v>
       </c>
       <c r="Q78">
-        <v>-1.8040743424</v>
+        <v>-1.8537640048</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1619001529678291</v>
+        <v>0.1669479857055608</v>
       </c>
       <c r="T78">
-        <v>2.681296835284738</v>
+        <v>2.797874958557987</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0643795139930247</v>
+        <v>0.0635434164086997</v>
       </c>
       <c r="W78">
-        <v>0.2206193106004448</v>
+        <v>0.2208164624108286</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2495329999729639</v>
+        <v>0.2462923116616267</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.208426712768617</v>
+        <v>0.210326712768617</v>
       </c>
       <c r="C79">
-        <v>-17.50498489012976</v>
+        <v>-17.83401179539087</v>
       </c>
       <c r="D79">
-        <v>3.899015109870234</v>
+        <v>3.853988204609132</v>
       </c>
       <c r="E79">
-        <v>3.968</v>
+        <v>4.252000000000002</v>
       </c>
       <c r="F79">
-        <v>21.868</v>
+        <v>22.152</v>
       </c>
       <c r="G79">
         <v>0.464</v>
@@ -7765,37 +7765,37 @@
         <v>1.27</v>
       </c>
       <c r="M79">
-        <v>5.1564744</v>
+        <v>5.2234416</v>
       </c>
       <c r="N79">
-        <v>-3.8864744</v>
+        <v>-3.953441600000001</v>
       </c>
       <c r="O79">
-        <v>-1.0027103952</v>
+        <v>-1.0199879328</v>
       </c>
       <c r="P79">
-        <v>-2.8837640048</v>
+        <v>-2.9334536672</v>
       </c>
       <c r="Q79">
-        <v>-1.8537640048</v>
+        <v>-1.9034536672</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1669479857055608</v>
+        <v>0.1724547123285409</v>
       </c>
       <c r="T79">
-        <v>2.797874958557987</v>
+        <v>2.925051093037897</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0635434164086997</v>
+        <v>0.06272875722397278</v>
       </c>
       <c r="W79">
-        <v>0.2208164624108286</v>
+        <v>0.2210085590465872</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2462923116616267</v>
+        <v>0.2431347179223751</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.210326712768617</v>
+        <v>0.212226712768617</v>
       </c>
       <c r="C80">
-        <v>-17.83401179539087</v>
+        <v>-18.1620106070416</v>
       </c>
       <c r="D80">
-        <v>3.853988204609132</v>
+        <v>3.809989392958395</v>
       </c>
       <c r="E80">
-        <v>4.252000000000002</v>
+        <v>4.536000000000001</v>
       </c>
       <c r="F80">
-        <v>22.152</v>
+        <v>22.436</v>
       </c>
       <c r="G80">
         <v>0.464</v>
@@ -7847,37 +7847,37 @@
         <v>1.27</v>
       </c>
       <c r="M80">
-        <v>5.2234416</v>
+        <v>5.2904088</v>
       </c>
       <c r="N80">
-        <v>-3.953441600000001</v>
+        <v>-4.0204088</v>
       </c>
       <c r="O80">
-        <v>-1.0199879328</v>
+        <v>-1.0372654704</v>
       </c>
       <c r="P80">
-        <v>-2.9334536672</v>
+        <v>-2.9831433296</v>
       </c>
       <c r="Q80">
-        <v>-1.9034536672</v>
+        <v>-1.9531433296</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1724547123285409</v>
+        <v>0.1784858891060905</v>
       </c>
       <c r="T80">
-        <v>2.925051093037897</v>
+        <v>3.064339240325416</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06272875722397278</v>
+        <v>0.06193472232240351</v>
       </c>
       <c r="W80">
-        <v>0.2210085590465872</v>
+        <v>0.2211957924763773</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2431347179223751</v>
+        <v>0.2400570632651299</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.212226712768617</v>
+        <v>0.2141267127686171</v>
       </c>
       <c r="C81">
-        <v>-18.1620106070416</v>
+        <v>-18.48901613912594</v>
       </c>
       <c r="D81">
-        <v>3.809989392958395</v>
+        <v>3.766983860874064</v>
       </c>
       <c r="E81">
-        <v>4.536000000000001</v>
+        <v>4.82</v>
       </c>
       <c r="F81">
-        <v>22.436</v>
+        <v>22.72</v>
       </c>
       <c r="G81">
         <v>0.464</v>
@@ -7929,37 +7929,37 @@
         <v>1.27</v>
       </c>
       <c r="M81">
-        <v>5.2904088</v>
+        <v>5.357376</v>
       </c>
       <c r="N81">
-        <v>-4.0204088</v>
+        <v>-4.087376000000001</v>
       </c>
       <c r="O81">
-        <v>-1.0372654704</v>
+        <v>-1.054543008</v>
       </c>
       <c r="P81">
-        <v>-2.9831433296</v>
+        <v>-3.032832992</v>
       </c>
       <c r="Q81">
-        <v>-1.9531433296</v>
+        <v>-2.002832992</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1784858891060905</v>
+        <v>0.185120183561395</v>
       </c>
       <c r="T81">
-        <v>3.064339240325416</v>
+        <v>3.217556202341687</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06193472232240351</v>
+        <v>0.06116053829337346</v>
       </c>
       <c r="W81">
-        <v>0.2211957924763773</v>
+        <v>0.2213783450704226</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2400570632651299</v>
+        <v>0.2370563499743157</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2141267127686171</v>
+        <v>0.216026712768617</v>
       </c>
       <c r="C82">
-        <v>-18.48901613912594</v>
+        <v>-18.81506165136813</v>
       </c>
       <c r="D82">
-        <v>3.766983860874064</v>
+        <v>3.724938348631875</v>
       </c>
       <c r="E82">
-        <v>4.82</v>
+        <v>5.104000000000003</v>
       </c>
       <c r="F82">
-        <v>22.72</v>
+        <v>23.004</v>
       </c>
       <c r="G82">
         <v>0.464</v>
@@ -8011,37 +8011,37 @@
         <v>1.27</v>
       </c>
       <c r="M82">
-        <v>5.357376</v>
+        <v>5.424343200000001</v>
       </c>
       <c r="N82">
-        <v>-4.087376000000001</v>
+        <v>-4.154343200000001</v>
       </c>
       <c r="O82">
-        <v>-1.054543008</v>
+        <v>-1.0718205456</v>
       </c>
       <c r="P82">
-        <v>-3.032832992</v>
+        <v>-3.082522654400001</v>
       </c>
       <c r="Q82">
-        <v>-2.002832992</v>
+        <v>-2.052522654400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.185120183561395</v>
+        <v>0.1924528248014684</v>
       </c>
       <c r="T82">
-        <v>3.217556202341687</v>
+        <v>3.386901265622828</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06116053829337346</v>
+        <v>0.06040546991938119</v>
       </c>
       <c r="W82">
-        <v>0.2213783450704226</v>
+        <v>0.2215563901930099</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2370563499743157</v>
+        <v>0.2341297283696945</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.216026712768617</v>
+        <v>0.2179267127686171</v>
       </c>
       <c r="C83">
-        <v>-18.81506165136813</v>
+        <v>-19.14017893495858</v>
       </c>
       <c r="D83">
-        <v>3.724938348631875</v>
+        <v>3.683821065041414</v>
       </c>
       <c r="E83">
-        <v>5.104000000000003</v>
+        <v>5.388000000000002</v>
       </c>
       <c r="F83">
-        <v>23.004</v>
+        <v>23.288</v>
       </c>
       <c r="G83">
         <v>0.464</v>
@@ -8093,37 +8093,37 @@
         <v>1.27</v>
       </c>
       <c r="M83">
-        <v>5.424343200000001</v>
+        <v>5.491310400000001</v>
       </c>
       <c r="N83">
-        <v>-4.154343200000001</v>
+        <v>-4.221310400000001</v>
       </c>
       <c r="O83">
-        <v>-1.0718205456</v>
+        <v>-1.0890980832</v>
       </c>
       <c r="P83">
-        <v>-3.082522654400001</v>
+        <v>-3.1322123168</v>
       </c>
       <c r="Q83">
-        <v>-2.052522654400001</v>
+        <v>-2.1022123168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1924528248014684</v>
+        <v>0.2006002039571056</v>
       </c>
       <c r="T83">
-        <v>3.386901265622828</v>
+        <v>3.575062447046319</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06040546991938119</v>
+        <v>0.05966881784719361</v>
       </c>
       <c r="W83">
-        <v>0.2215563901930099</v>
+        <v>0.2217300927516318</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2341297283696945</v>
+        <v>0.2312744877798202</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2179267127686171</v>
+        <v>0.219826712768617</v>
       </c>
       <c r="C84">
-        <v>-19.14017893495858</v>
+        <v>-19.46439839272013</v>
       </c>
       <c r="D84">
-        <v>3.683821065041414</v>
+        <v>3.643601607279866</v>
       </c>
       <c r="E84">
-        <v>5.388000000000002</v>
+        <v>5.672000000000001</v>
       </c>
       <c r="F84">
-        <v>23.288</v>
+        <v>23.572</v>
       </c>
       <c r="G84">
         <v>0.464</v>
@@ -8175,37 +8175,37 @@
         <v>1.27</v>
       </c>
       <c r="M84">
-        <v>5.491310400000001</v>
+        <v>5.5582776</v>
       </c>
       <c r="N84">
-        <v>-4.221310400000001</v>
+        <v>-4.288277600000001</v>
       </c>
       <c r="O84">
-        <v>-1.0890980832</v>
+        <v>-1.1063756208</v>
       </c>
       <c r="P84">
-        <v>-3.1322123168</v>
+        <v>-3.181901979200001</v>
       </c>
       <c r="Q84">
-        <v>-2.1022123168</v>
+        <v>-2.151901979200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2006002039571056</v>
+        <v>0.2097060983075235</v>
       </c>
       <c r="T84">
-        <v>3.575062447046319</v>
+        <v>3.785360238049043</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05966881784719361</v>
+        <v>0.05894991642734791</v>
       </c>
       <c r="W84">
-        <v>0.2217300927516318</v>
+        <v>0.2218996097064314</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2312744877798202</v>
+        <v>0.2284880481680152</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.219826712768617</v>
+        <v>0.2217267127686171</v>
       </c>
       <c r="C85">
-        <v>-19.46439839272013</v>
+        <v>-19.78774911407953</v>
       </c>
       <c r="D85">
-        <v>3.643601607279866</v>
+        <v>3.604250885920474</v>
       </c>
       <c r="E85">
-        <v>5.672000000000001</v>
+        <v>5.956000000000003</v>
       </c>
       <c r="F85">
-        <v>23.572</v>
+        <v>23.856</v>
       </c>
       <c r="G85">
         <v>0.464</v>
@@ -8257,37 +8257,37 @@
         <v>1.27</v>
       </c>
       <c r="M85">
-        <v>5.5582776</v>
+        <v>5.625244800000001</v>
       </c>
       <c r="N85">
-        <v>-4.288277600000001</v>
+        <v>-4.355244800000001</v>
       </c>
       <c r="O85">
-        <v>-1.1063756208</v>
+        <v>-1.1236531584</v>
       </c>
       <c r="P85">
-        <v>-3.181901979200001</v>
+        <v>-3.231591641600001</v>
       </c>
       <c r="Q85">
-        <v>-2.151901979200001</v>
+        <v>-2.2015916416</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2097060983075235</v>
+        <v>0.2199502294517438</v>
       </c>
       <c r="T85">
-        <v>3.785360238049043</v>
+        <v>4.021945252927109</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05894991642734791</v>
+        <v>0.05824813170797472</v>
       </c>
       <c r="W85">
-        <v>0.2218996097064314</v>
+        <v>0.2220650905432596</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2284880481680152</v>
+        <v>0.2257679523564912</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.221726712768617</v>
+        <v>0.223626712768617</v>
       </c>
       <c r="C86">
-        <v>-19.78774911407952</v>
+        <v>-20.11025894523273</v>
       </c>
       <c r="D86">
-        <v>3.604250885920474</v>
+        <v>3.565741054767269</v>
       </c>
       <c r="E86">
-        <v>5.956</v>
+        <v>6.239999999999998</v>
       </c>
       <c r="F86">
-        <v>23.856</v>
+        <v>24.14</v>
       </c>
       <c r="G86">
         <v>0.464</v>
@@ -8339,37 +8339,37 @@
         <v>1.27</v>
       </c>
       <c r="M86">
-        <v>5.6252448</v>
+        <v>5.692212</v>
       </c>
       <c r="N86">
-        <v>-4.3552448</v>
+        <v>-4.422212</v>
       </c>
       <c r="O86">
-        <v>-1.1236531584</v>
+        <v>-1.140930696</v>
       </c>
       <c r="P86">
-        <v>-3.231591641600001</v>
+        <v>-3.281281304</v>
       </c>
       <c r="Q86">
-        <v>-2.2015916416</v>
+        <v>-2.251281304</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2199502294517437</v>
+        <v>0.2315602447485266</v>
       </c>
       <c r="T86">
-        <v>4.021945252927106</v>
+        <v>4.29007493645558</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05824813170797473</v>
+        <v>0.05756285957023385</v>
       </c>
       <c r="W86">
-        <v>0.2220650905432596</v>
+        <v>0.2222266777133389</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2257679523564912</v>
+        <v>0.223111858799356</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.223626712768617</v>
+        <v>0.225526712768617</v>
       </c>
       <c r="C87">
-        <v>-20.11025894523273</v>
+        <v>-20.43195455485967</v>
       </c>
       <c r="D87">
-        <v>3.565741054767269</v>
+        <v>3.528045445140334</v>
       </c>
       <c r="E87">
-        <v>6.239999999999998</v>
+        <v>6.524000000000001</v>
       </c>
       <c r="F87">
-        <v>24.14</v>
+        <v>24.424</v>
       </c>
       <c r="G87">
         <v>0.464</v>
@@ -8421,37 +8421,37 @@
         <v>1.27</v>
       </c>
       <c r="M87">
-        <v>5.692212</v>
+        <v>5.7591792</v>
       </c>
       <c r="N87">
-        <v>-4.422212</v>
+        <v>-4.489179200000001</v>
       </c>
       <c r="O87">
-        <v>-1.140930696</v>
+        <v>-1.1582082336</v>
       </c>
       <c r="P87">
-        <v>-3.281281304</v>
+        <v>-3.330970966400001</v>
       </c>
       <c r="Q87">
-        <v>-2.251281304</v>
+        <v>-2.3009709664</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2315602447485266</v>
+        <v>0.2448288336591356</v>
       </c>
       <c r="T87">
-        <v>4.29007493645558</v>
+        <v>4.596508860488122</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05756285957023385</v>
+        <v>0.05689352399383578</v>
       </c>
       <c r="W87">
-        <v>0.2222266777133389</v>
+        <v>0.2223845070422535</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.223111858799356</v>
+        <v>0.2205175348598285</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.225526712768617</v>
+        <v>0.227426712768617</v>
       </c>
       <c r="C88">
-        <v>-20.43195455485967</v>
+        <v>-20.75286149571426</v>
       </c>
       <c r="D88">
-        <v>3.528045445140334</v>
+        <v>3.491138504285737</v>
       </c>
       <c r="E88">
-        <v>6.524000000000001</v>
+        <v>6.808</v>
       </c>
       <c r="F88">
-        <v>24.424</v>
+        <v>24.708</v>
       </c>
       <c r="G88">
         <v>0.464</v>
@@ -8503,37 +8503,37 @@
         <v>1.27</v>
       </c>
       <c r="M88">
-        <v>5.7591792</v>
+        <v>5.8261464</v>
       </c>
       <c r="N88">
-        <v>-4.489179200000001</v>
+        <v>-4.5561464</v>
       </c>
       <c r="O88">
-        <v>-1.1582082336</v>
+        <v>-1.1754857712</v>
       </c>
       <c r="P88">
-        <v>-3.330970966400001</v>
+        <v>-3.3806606288</v>
       </c>
       <c r="Q88">
-        <v>-2.3009709664</v>
+        <v>-2.3506606288</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2448288336591356</v>
+        <v>0.2601387439406076</v>
       </c>
       <c r="T88">
-        <v>4.596508860488122</v>
+        <v>4.950086465141054</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05689352399383578</v>
+        <v>0.0562395754421825</v>
       </c>
       <c r="W88">
-        <v>0.2223845070422535</v>
+        <v>0.2225387081107334</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2205175348598285</v>
+        <v>0.2179828505510949</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.227426712768617</v>
+        <v>0.229326712768617</v>
       </c>
       <c r="C89">
-        <v>-20.75286149571426</v>
+        <v>-21.07300426238881</v>
       </c>
       <c r="D89">
-        <v>3.491138504285737</v>
+        <v>3.454995737611188</v>
       </c>
       <c r="E89">
-        <v>6.808</v>
+        <v>7.091999999999999</v>
       </c>
       <c r="F89">
-        <v>24.708</v>
+        <v>24.992</v>
       </c>
       <c r="G89">
         <v>0.464</v>
@@ -8585,37 +8585,37 @@
         <v>1.27</v>
       </c>
       <c r="M89">
-        <v>5.8261464</v>
+        <v>5.8931136</v>
       </c>
       <c r="N89">
-        <v>-4.5561464</v>
+        <v>-4.6231136</v>
       </c>
       <c r="O89">
-        <v>-1.1754857712</v>
+        <v>-1.1927633088</v>
       </c>
       <c r="P89">
-        <v>-3.3806606288</v>
+        <v>-3.4303502912</v>
       </c>
       <c r="Q89">
-        <v>-2.3506606288</v>
+        <v>-2.4003502912</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2601387439406076</v>
+        <v>0.2780003059356583</v>
       </c>
       <c r="T89">
-        <v>4.950086465141054</v>
+        <v>5.362593670569476</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0562395754421825</v>
+        <v>0.05560048935761225</v>
       </c>
       <c r="W89">
-        <v>0.2225387081107334</v>
+        <v>0.222689404609475</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2179828505510949</v>
+        <v>0.2155057727039233</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.229326712768617</v>
+        <v>0.2312267127686171</v>
       </c>
       <c r="C90">
-        <v>-21.07300426238881</v>
+        <v>-21.39240634552692</v>
       </c>
       <c r="D90">
-        <v>3.454995737611188</v>
+        <v>3.419593654473077</v>
       </c>
       <c r="E90">
-        <v>7.091999999999999</v>
+        <v>7.376000000000001</v>
       </c>
       <c r="F90">
-        <v>24.992</v>
+        <v>25.276</v>
       </c>
       <c r="G90">
         <v>0.464</v>
@@ -8667,37 +8667,37 @@
         <v>1.27</v>
       </c>
       <c r="M90">
-        <v>5.8931136</v>
+        <v>5.9600808</v>
       </c>
       <c r="N90">
-        <v>-4.6231136</v>
+        <v>-4.6900808</v>
       </c>
       <c r="O90">
-        <v>-1.1927633088</v>
+        <v>-1.2100408464</v>
       </c>
       <c r="P90">
-        <v>-3.4303502912</v>
+        <v>-3.4800399536</v>
       </c>
       <c r="Q90">
-        <v>-2.4003502912</v>
+        <v>-2.4500399536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2780003059356583</v>
+        <v>0.2991094246570818</v>
       </c>
       <c r="T90">
-        <v>5.362593670569476</v>
+        <v>5.850102186075793</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05560048935761225</v>
+        <v>0.05497576475808851</v>
       </c>
       <c r="W90">
-        <v>0.222689404609475</v>
+        <v>0.2228367146700427</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2155057727039233</v>
+        <v>0.2130843595274748</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2312267127686171</v>
+        <v>0.233126712768617</v>
       </c>
       <c r="C91">
-        <v>-21.39240634552692</v>
+        <v>-21.71109028273733</v>
       </c>
       <c r="D91">
-        <v>3.419593654473077</v>
+        <v>3.384909717262668</v>
       </c>
       <c r="E91">
-        <v>7.376000000000001</v>
+        <v>7.66</v>
       </c>
       <c r="F91">
-        <v>25.276</v>
+        <v>25.56</v>
       </c>
       <c r="G91">
         <v>0.464</v>
@@ -8749,37 +8749,37 @@
         <v>1.27</v>
       </c>
       <c r="M91">
-        <v>5.9600808</v>
+        <v>6.027048</v>
       </c>
       <c r="N91">
-        <v>-4.6900808</v>
+        <v>-4.757048</v>
       </c>
       <c r="O91">
-        <v>-1.2100408464</v>
+        <v>-1.227318384</v>
       </c>
       <c r="P91">
-        <v>-3.4800399536</v>
+        <v>-3.529729616</v>
       </c>
       <c r="Q91">
-        <v>-2.4500399536</v>
+        <v>-2.499729616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2991094246570818</v>
+        <v>0.32444036712279</v>
       </c>
       <c r="T91">
-        <v>5.850102186075793</v>
+        <v>6.435112404683372</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05497576475808851</v>
+        <v>0.05436492292744308</v>
       </c>
       <c r="W91">
-        <v>0.2228367146700427</v>
+        <v>0.2229807511737089</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2130843595274748</v>
+        <v>0.2107167555327251</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.233126712768617</v>
+        <v>0.235026712768617</v>
       </c>
       <c r="C92">
-        <v>-21.71109028273733</v>
+        <v>-22.02907770644036</v>
       </c>
       <c r="D92">
-        <v>3.384909717262668</v>
+        <v>3.350922293559635</v>
       </c>
       <c r="E92">
-        <v>7.66</v>
+        <v>7.944000000000003</v>
       </c>
       <c r="F92">
-        <v>25.56</v>
+        <v>25.844</v>
       </c>
       <c r="G92">
         <v>0.464</v>
@@ -8831,37 +8831,37 @@
         <v>1.27</v>
       </c>
       <c r="M92">
-        <v>6.027048</v>
+        <v>6.0940152</v>
       </c>
       <c r="N92">
-        <v>-4.757048</v>
+        <v>-4.824015200000001</v>
       </c>
       <c r="O92">
-        <v>-1.227318384</v>
+        <v>-1.2445959216</v>
       </c>
       <c r="P92">
-        <v>-3.529729616</v>
+        <v>-3.579419278400001</v>
       </c>
       <c r="Q92">
-        <v>-2.499729616</v>
+        <v>-2.5494192784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.32444036712279</v>
+        <v>0.3554004079142111</v>
       </c>
       <c r="T92">
-        <v>6.435112404683372</v>
+        <v>7.150124894092637</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05436492292744308</v>
+        <v>0.05376750619197667</v>
       </c>
       <c r="W92">
-        <v>0.2229807511737089</v>
+        <v>0.2231216220399319</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2107167555327251</v>
+        <v>0.2084011867906072</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.235026712768617</v>
+        <v>0.236926712768617</v>
       </c>
       <c r="C93">
-        <v>-22.02907770644036</v>
+        <v>-22.34638938886055</v>
       </c>
       <c r="D93">
-        <v>3.350922293559635</v>
+        <v>3.317610611139445</v>
       </c>
       <c r="E93">
-        <v>7.944000000000003</v>
+        <v>8.228000000000002</v>
       </c>
       <c r="F93">
-        <v>25.844</v>
+        <v>26.128</v>
       </c>
       <c r="G93">
         <v>0.464</v>
@@ -8913,37 +8913,37 @@
         <v>1.27</v>
       </c>
       <c r="M93">
-        <v>6.0940152</v>
+        <v>6.1609824</v>
       </c>
       <c r="N93">
-        <v>-4.824015200000001</v>
+        <v>-4.8909824</v>
       </c>
       <c r="O93">
-        <v>-1.2445959216</v>
+        <v>-1.2618734592</v>
       </c>
       <c r="P93">
-        <v>-3.579419278400001</v>
+        <v>-3.6291089408</v>
       </c>
       <c r="Q93">
-        <v>-2.5494192784</v>
+        <v>-2.5991089408</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3554004079142111</v>
+        <v>0.3941004589034876</v>
       </c>
       <c r="T93">
-        <v>7.150124894092637</v>
+        <v>8.043890505854218</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05376750619197667</v>
+        <v>0.05318307677684649</v>
       </c>
       <c r="W93">
-        <v>0.2231216220399319</v>
+        <v>0.2232594304960196</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2084011867906072</v>
+        <v>0.206135956499405</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.236926712768617</v>
+        <v>0.238826712768617</v>
       </c>
       <c r="C94">
-        <v>-22.34638938886055</v>
+        <v>-22.66304528436203</v>
       </c>
       <c r="D94">
-        <v>3.317610611139445</v>
+        <v>3.284954715637972</v>
       </c>
       <c r="E94">
-        <v>8.228000000000002</v>
+        <v>8.512</v>
       </c>
       <c r="F94">
-        <v>26.128</v>
+        <v>26.412</v>
       </c>
       <c r="G94">
         <v>0.464</v>
@@ -8995,37 +8995,37 @@
         <v>1.27</v>
       </c>
       <c r="M94">
-        <v>6.1609824</v>
+        <v>6.2279496</v>
       </c>
       <c r="N94">
-        <v>-4.8909824</v>
+        <v>-4.9579496</v>
       </c>
       <c r="O94">
-        <v>-1.2618734592</v>
+        <v>-1.2791509968</v>
       </c>
       <c r="P94">
-        <v>-3.6291089408</v>
+        <v>-3.6787986032</v>
       </c>
       <c r="Q94">
-        <v>-2.5991089408</v>
+        <v>-2.648798603199999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3941004589034876</v>
+        <v>0.4438576673182716</v>
       </c>
       <c r="T94">
-        <v>8.043890505854218</v>
+        <v>9.19301772097625</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05318307677684649</v>
+        <v>0.05261121573623524</v>
       </c>
       <c r="W94">
-        <v>0.2232594304960196</v>
+        <v>0.2233942753293957</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.206135956499405</v>
+        <v>0.2039194408381211</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.238826712768617</v>
+        <v>0.240726712768617</v>
       </c>
       <c r="C95">
-        <v>-22.66304528436203</v>
+        <v>-22.97906456930796</v>
       </c>
       <c r="D95">
-        <v>3.284954715637972</v>
+        <v>3.252935430692039</v>
       </c>
       <c r="E95">
-        <v>8.512</v>
+        <v>8.796000000000003</v>
       </c>
       <c r="F95">
-        <v>26.412</v>
+        <v>26.696</v>
       </c>
       <c r="G95">
         <v>0.464</v>
@@ -9077,37 +9077,37 @@
         <v>1.27</v>
       </c>
       <c r="M95">
-        <v>6.2279496</v>
+        <v>6.2949168</v>
       </c>
       <c r="N95">
-        <v>-4.9579496</v>
+        <v>-5.024916800000001</v>
       </c>
       <c r="O95">
-        <v>-1.2791509968</v>
+        <v>-1.2964285344</v>
       </c>
       <c r="P95">
-        <v>-3.6787986032</v>
+        <v>-3.7284882656</v>
       </c>
       <c r="Q95">
-        <v>-2.648798603199999</v>
+        <v>-2.6984882656</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4438576673182716</v>
+        <v>0.5102006118713169</v>
       </c>
       <c r="T95">
-        <v>9.19301772097625</v>
+        <v>10.72518734113896</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05261121573623524</v>
+        <v>0.0520515219518072</v>
       </c>
       <c r="W95">
-        <v>0.2233942753293957</v>
+        <v>0.2235262511237639</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2039194408381211</v>
+        <v>0.201750085084524</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.240726712768617</v>
+        <v>0.2426267127686171</v>
       </c>
       <c r="C96">
-        <v>-22.97906456930796</v>
+        <v>-23.29446567961142</v>
       </c>
       <c r="D96">
-        <v>3.252935430692039</v>
+        <v>3.221534320388579</v>
       </c>
       <c r="E96">
-        <v>8.796000000000003</v>
+        <v>9.080000000000002</v>
       </c>
       <c r="F96">
-        <v>26.696</v>
+        <v>26.98</v>
       </c>
       <c r="G96">
         <v>0.464</v>
@@ -9159,37 +9159,37 @@
         <v>1.27</v>
       </c>
       <c r="M96">
-        <v>6.2949168</v>
+        <v>6.361884000000001</v>
       </c>
       <c r="N96">
-        <v>-5.024916800000001</v>
+        <v>-5.091884000000001</v>
       </c>
       <c r="O96">
-        <v>-1.2964285344</v>
+        <v>-1.313706072</v>
       </c>
       <c r="P96">
-        <v>-3.7284882656</v>
+        <v>-3.778177928000001</v>
       </c>
       <c r="Q96">
-        <v>-2.6984882656</v>
+        <v>-2.748177928</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5102006118713169</v>
+        <v>0.6030807342455806</v>
       </c>
       <c r="T96">
-        <v>10.72518734113896</v>
+        <v>12.87022480936676</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0520515219518072</v>
+        <v>0.05150361119441976</v>
       </c>
       <c r="W96">
-        <v>0.2235262511237639</v>
+        <v>0.2236554484803558</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.201750085084524</v>
+        <v>0.1996263999783711</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2426267127686171</v>
+        <v>0.2445267127686171</v>
       </c>
       <c r="C97">
-        <v>-23.29446567961142</v>
+        <v>-23.60926634613211</v>
       </c>
       <c r="D97">
-        <v>3.221534320388579</v>
+        <v>3.190733653867891</v>
       </c>
       <c r="E97">
-        <v>9.080000000000002</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="F97">
-        <v>26.98</v>
+        <v>27.264</v>
       </c>
       <c r="G97">
         <v>0.464</v>
@@ -9241,37 +9241,37 @@
         <v>1.27</v>
       </c>
       <c r="M97">
-        <v>6.361884000000001</v>
+        <v>6.4288512</v>
       </c>
       <c r="N97">
-        <v>-5.091884000000001</v>
+        <v>-5.158851200000001</v>
       </c>
       <c r="O97">
-        <v>-1.313706072</v>
+        <v>-1.3309836096</v>
       </c>
       <c r="P97">
-        <v>-3.778177928000001</v>
+        <v>-3.8278675904</v>
       </c>
       <c r="Q97">
-        <v>-2.748177928</v>
+        <v>-2.7978675904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6030807342455806</v>
+        <v>0.742400917806976</v>
       </c>
       <c r="T97">
-        <v>12.87022480936676</v>
+        <v>16.08778101170846</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05150361119441976</v>
+        <v>0.05096711524447788</v>
       </c>
       <c r="W97">
-        <v>0.2236554484803558</v>
+        <v>0.2237819542253521</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1996263999783711</v>
+        <v>0.1975469583119297</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.244526712768617</v>
+        <v>0.2464267127686171</v>
       </c>
       <c r="C98">
-        <v>-23.60926634613211</v>
+        <v>-23.92348362806176</v>
       </c>
       <c r="D98">
-        <v>3.190733653867891</v>
+        <v>3.160516371938239</v>
       </c>
       <c r="E98">
-        <v>9.364000000000001</v>
+        <v>9.648</v>
       </c>
       <c r="F98">
-        <v>27.264</v>
+        <v>27.548</v>
       </c>
       <c r="G98">
         <v>0.464</v>
@@ -9323,37 +9323,37 @@
         <v>1.27</v>
       </c>
       <c r="M98">
-        <v>6.4288512</v>
+        <v>6.4958184</v>
       </c>
       <c r="N98">
-        <v>-5.158851200000001</v>
+        <v>-5.225818400000001</v>
       </c>
       <c r="O98">
-        <v>-1.3309836096</v>
+        <v>-1.3482611472</v>
       </c>
       <c r="P98">
-        <v>-3.8278675904</v>
+        <v>-3.8775572528</v>
       </c>
       <c r="Q98">
-        <v>-2.7978675904</v>
+        <v>-2.847557252800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7424009178069741</v>
+        <v>0.9746012237426324</v>
       </c>
       <c r="T98">
-        <v>16.08778101170842</v>
+        <v>21.45037468227789</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05096711524447788</v>
+        <v>0.05044168106669977</v>
       </c>
       <c r="W98">
-        <v>0.2237819542253521</v>
+        <v>0.2239058516044722</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1975469583119297</v>
+        <v>0.1955103917313944</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2464267127686171</v>
+        <v>0.248326712768617</v>
       </c>
       <c r="C99">
-        <v>-23.92348362806176</v>
+        <v>-24.23713394443036</v>
       </c>
       <c r="D99">
-        <v>3.160516371938239</v>
+        <v>3.130866055569637</v>
       </c>
       <c r="E99">
-        <v>9.648</v>
+        <v>9.931999999999999</v>
       </c>
       <c r="F99">
-        <v>27.548</v>
+        <v>27.832</v>
       </c>
       <c r="G99">
         <v>0.464</v>
@@ -9405,37 +9405,37 @@
         <v>1.27</v>
       </c>
       <c r="M99">
-        <v>6.4958184</v>
+        <v>6.5627856</v>
       </c>
       <c r="N99">
-        <v>-5.225818400000001</v>
+        <v>-5.2927856</v>
       </c>
       <c r="O99">
-        <v>-1.3482611472</v>
+        <v>-1.3655386848</v>
       </c>
       <c r="P99">
-        <v>-3.8775572528</v>
+        <v>-3.9272469152</v>
       </c>
       <c r="Q99">
-        <v>-2.847557252800001</v>
+        <v>-2.8972469152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9746012237426324</v>
+        <v>1.439001835613948</v>
       </c>
       <c r="T99">
-        <v>21.45037468227789</v>
+        <v>32.17556202341683</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05044168106669977</v>
+        <v>0.04992697003540691</v>
       </c>
       <c r="W99">
-        <v>0.2239058516044722</v>
+        <v>0.2240272204656511</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1955103917313944</v>
+        <v>0.1935153877341352</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.248326712768617</v>
+        <v>0.250226712768617</v>
       </c>
       <c r="C100">
-        <v>-24.23713394443036</v>
+        <v>-24.55023310385536</v>
       </c>
       <c r="D100">
-        <v>3.130866055569637</v>
+        <v>3.101766896144639</v>
       </c>
       <c r="E100">
-        <v>9.931999999999999</v>
+        <v>10.216</v>
       </c>
       <c r="F100">
-        <v>27.832</v>
+        <v>28.116</v>
       </c>
       <c r="G100">
         <v>0.464</v>
@@ -9487,37 +9487,37 @@
         <v>1.27</v>
       </c>
       <c r="M100">
-        <v>6.5627856</v>
+        <v>6.6297528</v>
       </c>
       <c r="N100">
-        <v>-5.2927856</v>
+        <v>-5.359752800000001</v>
       </c>
       <c r="O100">
-        <v>-1.3655386848</v>
+        <v>-1.3828162224</v>
       </c>
       <c r="P100">
-        <v>-3.9272469152</v>
+        <v>-3.976936577600001</v>
       </c>
       <c r="Q100">
-        <v>-2.8972469152</v>
+        <v>-2.946936577600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.439001835613948</v>
+        <v>2.832203671227897</v>
       </c>
       <c r="T100">
-        <v>32.17556202341683</v>
+        <v>64.35112404683366</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04992697003540691</v>
+        <v>0.04942265720676643</v>
       </c>
       <c r="W100">
-        <v>0.2240272204656511</v>
+        <v>0.2241461374306445</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1935153877341352</v>
+        <v>0.1915606868479319</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.250226712768617</v>
-      </c>
-      <c r="C101">
-        <v>-24.55023310385536</v>
-      </c>
-      <c r="D101">
-        <v>3.101766896144639</v>
-      </c>
-      <c r="E101">
-        <v>10.216</v>
-      </c>
-      <c r="F101">
-        <v>28.116</v>
-      </c>
-      <c r="G101">
-        <v>0.464</v>
-      </c>
-      <c r="H101">
-        <v>10.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.3</v>
-      </c>
-      <c r="K101">
-        <v>1.03</v>
-      </c>
-      <c r="L101">
-        <v>1.27</v>
-      </c>
-      <c r="M101">
-        <v>6.6297528</v>
-      </c>
-      <c r="N101">
-        <v>-5.359752800000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.3828162224</v>
-      </c>
-      <c r="P101">
-        <v>-3.976936577600001</v>
-      </c>
-      <c r="Q101">
-        <v>-2.946936577600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.832203671227897</v>
-      </c>
-      <c r="T101">
-        <v>64.35112404683366</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04942265720676643</v>
-      </c>
-      <c r="W101">
-        <v>0.2241461374306445</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1915606868479319</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
